--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/10-base-limpa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/10-base-limpa.xlsx
@@ -756,6 +756,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1124,6 +1125,7 @@
       <c r="E34" s="8" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
@@ -1225,7 +1227,7 @@
     <row r="2">
       <c r="A2" s="9">
         <f>IF(B2="","",ROW()-1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>46023</v>
@@ -1263,7 +1265,7 @@
       </c>
       <c r="J2" s="14">
         <f>IF(OR(H2="",I2=""),"",H2*I2)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
@@ -1272,17 +1274,17 @@
       </c>
       <c r="L2" s="9">
         <f>IF(B2="","",MONTH(B2))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M2" s="9">
         <f>IF(B2="","",YEAR(B2))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9">
         <f>IF(B3="","",ROW()-1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B3" s="10" t="n">
         <v>46024</v>
@@ -1320,7 +1322,7 @@
       </c>
       <c r="J3" s="14">
         <f>IF(OR(H3="",I3=""),"",H3*I3)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K3" s="11" t="inlineStr">
         <is>
@@ -1329,17 +1331,17 @@
       </c>
       <c r="L3" s="9">
         <f>IF(B3="","",MONTH(B3))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M3" s="9">
         <f>IF(B3="","",YEAR(B3))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9">
         <f>IF(B4="","",ROW()-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>46024</v>
@@ -1377,7 +1379,7 @@
       </c>
       <c r="J4" s="14">
         <f>IF(OR(H4="",I4=""),"",H4*I4)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -1386,17 +1388,17 @@
       </c>
       <c r="L4" s="9">
         <f>IF(B4="","",MONTH(B4))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M4" s="9">
         <f>IF(B4="","",YEAR(B4))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9">
         <f>IF(B5="","",ROW()-1)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>46027</v>
@@ -1434,7 +1436,7 @@
       </c>
       <c r="J5" s="14">
         <f>IF(OR(H5="",I5=""),"",H5*I5)</f>
-        <v/>
+        <v>7200</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -1443,17 +1445,17 @@
       </c>
       <c r="L5" s="9">
         <f>IF(B5="","",MONTH(B5))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M5" s="9">
         <f>IF(B5="","",YEAR(B5))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9">
         <f>IF(B6="","",ROW()-1)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>46029</v>
@@ -1491,7 +1493,7 @@
       </c>
       <c r="J6" s="14">
         <f>IF(OR(H6="",I6=""),"",H6*I6)</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -1500,17 +1502,17 @@
       </c>
       <c r="L6" s="9">
         <f>IF(B6="","",MONTH(B6))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M6" s="9">
         <f>IF(B6="","",YEAR(B6))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9">
         <f>IF(B7="","",ROW()-1)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>46032</v>
@@ -1548,7 +1550,7 @@
       </c>
       <c r="J7" s="14">
         <f>IF(OR(H7="",I7=""),"",H7*I7)</f>
-        <v/>
+        <v>298</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1557,17 +1559,17 @@
       </c>
       <c r="L7" s="9">
         <f>IF(B7="","",MONTH(B7))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M7" s="9">
         <f>IF(B7="","",YEAR(B7))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9">
         <f>IF(B8="","",ROW()-1)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>46035</v>
@@ -1605,7 +1607,7 @@
       </c>
       <c r="J8" s="14">
         <f>IF(OR(H8="",I8=""),"",H8*I8)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
@@ -1614,17 +1616,17 @@
       </c>
       <c r="L8" s="9">
         <f>IF(B8="","",MONTH(B8))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M8" s="9">
         <f>IF(B8="","",YEAR(B8))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>IF(B9="","",ROW()-1)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>46036</v>
@@ -1662,7 +1664,7 @@
       </c>
       <c r="J9" s="14">
         <f>IF(OR(H9="",I9=""),"",H9*I9)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1671,17 +1673,17 @@
       </c>
       <c r="L9" s="9">
         <f>IF(B9="","",MONTH(B9))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M9" s="9">
         <f>IF(B9="","",YEAR(B9))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>IF(B10="","",ROW()-1)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>46036</v>
@@ -1719,7 +1721,7 @@
       </c>
       <c r="J10" s="14">
         <f>IF(OR(H10="",I10=""),"",H10*I10)</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
@@ -1728,17 +1730,17 @@
       </c>
       <c r="L10" s="9">
         <f>IF(B10="","",MONTH(B10))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M10" s="9">
         <f>IF(B10="","",YEAR(B10))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9">
         <f>IF(B11="","",ROW()-1)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>46037</v>
@@ -1776,7 +1778,7 @@
       </c>
       <c r="J11" s="14">
         <f>IF(OR(H11="",I11=""),"",H11*I11)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1785,17 +1787,17 @@
       </c>
       <c r="L11" s="9">
         <f>IF(B11="","",MONTH(B11))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M11" s="9">
         <f>IF(B11="","",YEAR(B11))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9">
         <f>IF(B12="","",ROW()-1)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>46038</v>
@@ -1833,7 +1835,7 @@
       </c>
       <c r="J12" s="14">
         <f>IF(OR(H12="",I12=""),"",H12*I12)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1842,17 +1844,17 @@
       </c>
       <c r="L12" s="9">
         <f>IF(B12="","",MONTH(B12))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M12" s="9">
         <f>IF(B12="","",YEAR(B12))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9">
         <f>IF(B13="","",ROW()-1)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>46038</v>
@@ -1890,7 +1892,7 @@
       </c>
       <c r="J13" s="14">
         <f>IF(OR(H13="",I13=""),"",H13*I13)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1899,17 +1901,17 @@
       </c>
       <c r="L13" s="9">
         <f>IF(B13="","",MONTH(B13))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M13" s="9">
         <f>IF(B13="","",YEAR(B13))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9">
         <f>IF(B14="","",ROW()-1)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>46038</v>
@@ -1947,7 +1949,7 @@
       </c>
       <c r="J14" s="14">
         <f>IF(OR(H14="",I14=""),"",H14*I14)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1956,17 +1958,17 @@
       </c>
       <c r="L14" s="9">
         <f>IF(B14="","",MONTH(B14))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M14" s="9">
         <f>IF(B14="","",YEAR(B14))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9">
         <f>IF(B15="","",ROW()-1)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>46041</v>
@@ -2004,7 +2006,7 @@
       </c>
       <c r="J15" s="14">
         <f>IF(OR(H15="",I15=""),"",H15*I15)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
@@ -2013,17 +2015,17 @@
       </c>
       <c r="L15" s="9">
         <f>IF(B15="","",MONTH(B15))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M15" s="9">
         <f>IF(B15="","",YEAR(B15))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9">
         <f>IF(B16="","",ROW()-1)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>46041</v>
@@ -2061,7 +2063,7 @@
       </c>
       <c r="J16" s="14">
         <f>IF(OR(H16="",I16=""),"",H16*I16)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
@@ -2070,17 +2072,17 @@
       </c>
       <c r="L16" s="9">
         <f>IF(B16="","",MONTH(B16))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M16" s="9">
         <f>IF(B16="","",YEAR(B16))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9">
         <f>IF(B17="","",ROW()-1)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>46042</v>
@@ -2118,7 +2120,7 @@
       </c>
       <c r="J17" s="14">
         <f>IF(OR(H17="",I17=""),"",H17*I17)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
@@ -2127,17 +2129,17 @@
       </c>
       <c r="L17" s="9">
         <f>IF(B17="","",MONTH(B17))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M17" s="9">
         <f>IF(B17="","",YEAR(B17))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9">
         <f>IF(B18="","",ROW()-1)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>46042</v>
@@ -2175,7 +2177,7 @@
       </c>
       <c r="J18" s="14">
         <f>IF(OR(H18="",I18=""),"",H18*I18)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -2184,17 +2186,17 @@
       </c>
       <c r="L18" s="9">
         <f>IF(B18="","",MONTH(B18))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M18" s="9">
         <f>IF(B18="","",YEAR(B18))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9">
         <f>IF(B19="","",ROW()-1)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>46050</v>
@@ -2232,7 +2234,7 @@
       </c>
       <c r="J19" s="14">
         <f>IF(OR(H19="",I19=""),"",H19*I19)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -2241,17 +2243,17 @@
       </c>
       <c r="L19" s="9">
         <f>IF(B19="","",MONTH(B19))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M19" s="9">
         <f>IF(B19="","",YEAR(B19))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9">
         <f>IF(B20="","",ROW()-1)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>46050</v>
@@ -2289,7 +2291,7 @@
       </c>
       <c r="J20" s="14">
         <f>IF(OR(H20="",I20=""),"",H20*I20)</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -2298,17 +2300,17 @@
       </c>
       <c r="L20" s="9">
         <f>IF(B20="","",MONTH(B20))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M20" s="9">
         <f>IF(B20="","",YEAR(B20))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9">
         <f>IF(B21="","",ROW()-1)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>46053</v>
@@ -2346,7 +2348,7 @@
       </c>
       <c r="J21" s="14">
         <f>IF(OR(H21="",I21=""),"",H21*I21)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -2355,17 +2357,17 @@
       </c>
       <c r="L21" s="9">
         <f>IF(B21="","",MONTH(B21))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M21" s="9">
         <f>IF(B21="","",YEAR(B21))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9">
         <f>IF(B22="","",ROW()-1)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>46055</v>
@@ -2403,7 +2405,7 @@
       </c>
       <c r="J22" s="14">
         <f>IF(OR(H22="",I22=""),"",H22*I22)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
@@ -2412,17 +2414,17 @@
       </c>
       <c r="L22" s="9">
         <f>IF(B22="","",MONTH(B22))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M22" s="9">
         <f>IF(B22="","",YEAR(B22))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9">
         <f>IF(B23="","",ROW()-1)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>46056</v>
@@ -2460,7 +2462,7 @@
       </c>
       <c r="J23" s="14">
         <f>IF(OR(H23="",I23=""),"",H23*I23)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
@@ -2469,17 +2471,17 @@
       </c>
       <c r="L23" s="9">
         <f>IF(B23="","",MONTH(B23))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M23" s="9">
         <f>IF(B23="","",YEAR(B23))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9">
         <f>IF(B24="","",ROW()-1)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>46057</v>
@@ -2517,7 +2519,7 @@
       </c>
       <c r="J24" s="14">
         <f>IF(OR(H24="",I24=""),"",H24*I24)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -2526,17 +2528,17 @@
       </c>
       <c r="L24" s="9">
         <f>IF(B24="","",MONTH(B24))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M24" s="9">
         <f>IF(B24="","",YEAR(B24))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9">
         <f>IF(B25="","",ROW()-1)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>46058</v>
@@ -2574,7 +2576,7 @@
       </c>
       <c r="J25" s="14">
         <f>IF(OR(H25="",I25=""),"",H25*I25)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2583,17 +2585,17 @@
       </c>
       <c r="L25" s="9">
         <f>IF(B25="","",MONTH(B25))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M25" s="9">
         <f>IF(B25="","",YEAR(B25))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9">
         <f>IF(B26="","",ROW()-1)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>46059</v>
@@ -2631,7 +2633,7 @@
       </c>
       <c r="J26" s="14">
         <f>IF(OR(H26="",I26=""),"",H26*I26)</f>
-        <v/>
+        <v>7200</v>
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
@@ -2640,17 +2642,17 @@
       </c>
       <c r="L26" s="9">
         <f>IF(B26="","",MONTH(B26))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M26" s="9">
         <f>IF(B26="","",YEAR(B26))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9">
         <f>IF(B27="","",ROW()-1)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>46062</v>
@@ -2688,7 +2690,7 @@
       </c>
       <c r="J27" s="14">
         <f>IF(OR(H27="",I27=""),"",H27*I27)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
@@ -2697,17 +2699,17 @@
       </c>
       <c r="L27" s="9">
         <f>IF(B27="","",MONTH(B27))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M27" s="9">
         <f>IF(B27="","",YEAR(B27))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9">
         <f>IF(B28="","",ROW()-1)</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>46067</v>
@@ -2745,7 +2747,7 @@
       </c>
       <c r="J28" s="14">
         <f>IF(OR(H28="",I28=""),"",H28*I28)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
@@ -2754,17 +2756,17 @@
       </c>
       <c r="L28" s="9">
         <f>IF(B28="","",MONTH(B28))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M28" s="9">
         <f>IF(B28="","",YEAR(B28))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9">
         <f>IF(B29="","",ROW()-1)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>46068</v>
@@ -2802,7 +2804,7 @@
       </c>
       <c r="J29" s="14">
         <f>IF(OR(H29="",I29=""),"",H29*I29)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
@@ -2811,17 +2813,17 @@
       </c>
       <c r="L29" s="9">
         <f>IF(B29="","",MONTH(B29))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M29" s="9">
         <f>IF(B29="","",YEAR(B29))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9">
         <f>IF(B30="","",ROW()-1)</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>46069</v>
@@ -2859,7 +2861,7 @@
       </c>
       <c r="J30" s="14">
         <f>IF(OR(H30="",I30=""),"",H30*I30)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
@@ -2868,17 +2870,17 @@
       </c>
       <c r="L30" s="9">
         <f>IF(B30="","",MONTH(B30))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M30" s="9">
         <f>IF(B30="","",YEAR(B30))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9">
         <f>IF(B31="","",ROW()-1)</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>46072</v>
@@ -2916,7 +2918,7 @@
       </c>
       <c r="J31" s="14">
         <f>IF(OR(H31="",I31=""),"",H31*I31)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
@@ -2925,17 +2927,17 @@
       </c>
       <c r="L31" s="9">
         <f>IF(B31="","",MONTH(B31))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M31" s="9">
         <f>IF(B31="","",YEAR(B31))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9">
         <f>IF(B32="","",ROW()-1)</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>46073</v>
@@ -2973,7 +2975,7 @@
       </c>
       <c r="J32" s="14">
         <f>IF(OR(H32="",I32=""),"",H32*I32)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
@@ -2982,17 +2984,17 @@
       </c>
       <c r="L32" s="9">
         <f>IF(B32="","",MONTH(B32))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M32" s="9">
         <f>IF(B32="","",YEAR(B32))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
         <f>IF(B33="","",ROW()-1)</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>46076</v>
@@ -3030,7 +3032,7 @@
       </c>
       <c r="J33" s="14">
         <f>IF(OR(H33="",I33=""),"",H33*I33)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
@@ -3039,17 +3041,17 @@
       </c>
       <c r="L33" s="9">
         <f>IF(B33="","",MONTH(B33))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M33" s="9">
         <f>IF(B33="","",YEAR(B33))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9">
         <f>IF(B34="","",ROW()-1)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>46077</v>
@@ -3087,7 +3089,7 @@
       </c>
       <c r="J34" s="14">
         <f>IF(OR(H34="",I34=""),"",H34*I34)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
@@ -3096,17 +3098,17 @@
       </c>
       <c r="L34" s="9">
         <f>IF(B34="","",MONTH(B34))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M34" s="9">
         <f>IF(B34="","",YEAR(B34))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
         <f>IF(B35="","",ROW()-1)</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>46078</v>
@@ -3144,7 +3146,7 @@
       </c>
       <c r="J35" s="14">
         <f>IF(OR(H35="",I35=""),"",H35*I35)</f>
-        <v/>
+        <v>147</v>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
@@ -3153,17 +3155,17 @@
       </c>
       <c r="L35" s="9">
         <f>IF(B35="","",MONTH(B35))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M35" s="9">
         <f>IF(B35="","",YEAR(B35))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
         <f>IF(B36="","",ROW()-1)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>46079</v>
@@ -3201,7 +3203,7 @@
       </c>
       <c r="J36" s="14">
         <f>IF(OR(H36="",I36=""),"",H36*I36)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
@@ -3210,17 +3212,17 @@
       </c>
       <c r="L36" s="9">
         <f>IF(B36="","",MONTH(B36))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M36" s="9">
         <f>IF(B36="","",YEAR(B36))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9">
         <f>IF(B37="","",ROW()-1)</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>46079</v>
@@ -3258,7 +3260,7 @@
       </c>
       <c r="J37" s="14">
         <f>IF(OR(H37="",I37=""),"",H37*I37)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K37" s="11" t="inlineStr">
         <is>
@@ -3267,17 +3269,17 @@
       </c>
       <c r="L37" s="9">
         <f>IF(B37="","",MONTH(B37))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M37" s="9">
         <f>IF(B37="","",YEAR(B37))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
         <f>IF(B38="","",ROW()-1)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>46080</v>
@@ -3315,7 +3317,7 @@
       </c>
       <c r="J38" s="14">
         <f>IF(OR(H38="",I38=""),"",H38*I38)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K38" s="11" t="inlineStr">
         <is>
@@ -3324,17 +3326,17 @@
       </c>
       <c r="L38" s="9">
         <f>IF(B38="","",MONTH(B38))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M38" s="9">
         <f>IF(B38="","",YEAR(B38))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
         <f>IF(B39="","",ROW()-1)</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>46081</v>
@@ -3372,7 +3374,7 @@
       </c>
       <c r="J39" s="14">
         <f>IF(OR(H39="",I39=""),"",H39*I39)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
@@ -3381,17 +3383,17 @@
       </c>
       <c r="L39" s="9">
         <f>IF(B39="","",MONTH(B39))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M39" s="9">
         <f>IF(B39="","",YEAR(B39))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9">
         <f>IF(B40="","",ROW()-1)</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="B40" s="10" t="n">
         <v>46081</v>
@@ -3429,7 +3431,7 @@
       </c>
       <c r="J40" s="14">
         <f>IF(OR(H40="",I40=""),"",H40*I40)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
@@ -3438,17 +3440,17 @@
       </c>
       <c r="L40" s="9">
         <f>IF(B40="","",MONTH(B40))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M40" s="9">
         <f>IF(B40="","",YEAR(B40))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9">
         <f>IF(B41="","",ROW()-1)</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>46085</v>
@@ -3486,7 +3488,7 @@
       </c>
       <c r="J41" s="14">
         <f>IF(OR(H41="",I41=""),"",H41*I41)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K41" s="11" t="inlineStr">
         <is>
@@ -3495,17 +3497,17 @@
       </c>
       <c r="L41" s="9">
         <f>IF(B41="","",MONTH(B41))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M41" s="9">
         <f>IF(B41="","",YEAR(B41))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9">
         <f>IF(B42="","",ROW()-1)</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>46090</v>
@@ -3543,7 +3545,7 @@
       </c>
       <c r="J42" s="14">
         <f>IF(OR(H42="",I42=""),"",H42*I42)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
@@ -3552,17 +3554,17 @@
       </c>
       <c r="L42" s="9">
         <f>IF(B42="","",MONTH(B42))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M42" s="9">
         <f>IF(B42="","",YEAR(B42))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9">
         <f>IF(B43="","",ROW()-1)</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>46091</v>
@@ -3600,7 +3602,7 @@
       </c>
       <c r="J43" s="14">
         <f>IF(OR(H43="",I43=""),"",H43*I43)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
@@ -3609,17 +3611,17 @@
       </c>
       <c r="L43" s="9">
         <f>IF(B43="","",MONTH(B43))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M43" s="9">
         <f>IF(B43="","",YEAR(B43))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9">
         <f>IF(B44="","",ROW()-1)</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>46091</v>
@@ -3657,7 +3659,7 @@
       </c>
       <c r="J44" s="14">
         <f>IF(OR(H44="",I44=""),"",H44*I44)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
@@ -3666,17 +3668,17 @@
       </c>
       <c r="L44" s="9">
         <f>IF(B44="","",MONTH(B44))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M44" s="9">
         <f>IF(B44="","",YEAR(B44))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9">
         <f>IF(B45="","",ROW()-1)</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>46092</v>
@@ -3714,7 +3716,7 @@
       </c>
       <c r="J45" s="14">
         <f>IF(OR(H45="",I45=""),"",H45*I45)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
@@ -3723,17 +3725,17 @@
       </c>
       <c r="L45" s="9">
         <f>IF(B45="","",MONTH(B45))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M45" s="9">
         <f>IF(B45="","",YEAR(B45))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9">
         <f>IF(B46="","",ROW()-1)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>46094</v>
@@ -3771,7 +3773,7 @@
       </c>
       <c r="J46" s="14">
         <f>IF(OR(H46="",I46=""),"",H46*I46)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -3780,17 +3782,17 @@
       </c>
       <c r="L46" s="9">
         <f>IF(B46="","",MONTH(B46))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M46" s="9">
         <f>IF(B46="","",YEAR(B46))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9">
         <f>IF(B47="","",ROW()-1)</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>46094</v>
@@ -3828,7 +3830,7 @@
       </c>
       <c r="J47" s="14">
         <f>IF(OR(H47="",I47=""),"",H47*I47)</f>
-        <v/>
+        <v>-400</v>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
@@ -3837,17 +3839,17 @@
       </c>
       <c r="L47" s="9">
         <f>IF(B47="","",MONTH(B47))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M47" s="9">
         <f>IF(B47="","",YEAR(B47))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9">
         <f>IF(B48="","",ROW()-1)</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>46095</v>
@@ -3885,7 +3887,7 @@
       </c>
       <c r="J48" s="14">
         <f>IF(OR(H48="",I48=""),"",H48*I48)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -3894,17 +3896,17 @@
       </c>
       <c r="L48" s="9">
         <f>IF(B48="","",MONTH(B48))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M48" s="9">
         <f>IF(B48="","",YEAR(B48))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9">
         <f>IF(B49="","",ROW()-1)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>46096</v>
@@ -3942,7 +3944,7 @@
       </c>
       <c r="J49" s="14">
         <f>IF(OR(H49="",I49=""),"",H49*I49)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
@@ -3951,17 +3953,17 @@
       </c>
       <c r="L49" s="9">
         <f>IF(B49="","",MONTH(B49))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M49" s="9">
         <f>IF(B49="","",YEAR(B49))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9">
         <f>IF(B50="","",ROW()-1)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>46096</v>
@@ -3999,7 +4001,7 @@
       </c>
       <c r="J50" s="14">
         <f>IF(OR(H50="",I50=""),"",H50*I50)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
@@ -4008,17 +4010,17 @@
       </c>
       <c r="L50" s="9">
         <f>IF(B50="","",MONTH(B50))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M50" s="9">
         <f>IF(B50="","",YEAR(B50))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9">
         <f>IF(B51="","",ROW()-1)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>46099</v>
@@ -4056,7 +4058,7 @@
       </c>
       <c r="J51" s="14">
         <f>IF(OR(H51="",I51=""),"",H51*I51)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
@@ -4065,17 +4067,17 @@
       </c>
       <c r="L51" s="9">
         <f>IF(B51="","",MONTH(B51))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M51" s="9">
         <f>IF(B51="","",YEAR(B51))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9">
         <f>IF(B52="","",ROW()-1)</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>46099</v>
@@ -4113,7 +4115,7 @@
       </c>
       <c r="J52" s="14">
         <f>IF(OR(H52="",I52=""),"",H52*I52)</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
@@ -4122,17 +4124,17 @@
       </c>
       <c r="L52" s="9">
         <f>IF(B52="","",MONTH(B52))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M52" s="9">
         <f>IF(B52="","",YEAR(B52))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9">
         <f>IF(B53="","",ROW()-1)</f>
-        <v/>
+        <v>52</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>46100</v>
@@ -4170,7 +4172,7 @@
       </c>
       <c r="J53" s="14">
         <f>IF(OR(H53="",I53=""),"",H53*I53)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
@@ -4179,17 +4181,17 @@
       </c>
       <c r="L53" s="9">
         <f>IF(B53="","",MONTH(B53))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M53" s="9">
         <f>IF(B53="","",YEAR(B53))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9">
         <f>IF(B54="","",ROW()-1)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>46100</v>
@@ -4227,7 +4229,7 @@
       </c>
       <c r="J54" s="14">
         <f>IF(OR(H54="",I54=""),"",H54*I54)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
@@ -4236,17 +4238,17 @@
       </c>
       <c r="L54" s="9">
         <f>IF(B54="","",MONTH(B54))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M54" s="9">
         <f>IF(B54="","",YEAR(B54))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9">
         <f>IF(B55="","",ROW()-1)</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>46102</v>
@@ -4284,7 +4286,7 @@
       </c>
       <c r="J55" s="14">
         <f>IF(OR(H55="",I55=""),"",H55*I55)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
@@ -4293,17 +4295,17 @@
       </c>
       <c r="L55" s="9">
         <f>IF(B55="","",MONTH(B55))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M55" s="9">
         <f>IF(B55="","",YEAR(B55))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9">
         <f>IF(B56="","",ROW()-1)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="B56" s="10" t="n">
         <v>46104</v>
@@ -4341,7 +4343,7 @@
       </c>
       <c r="J56" s="14">
         <f>IF(OR(H56="",I56=""),"",H56*I56)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
@@ -4350,17 +4352,17 @@
       </c>
       <c r="L56" s="9">
         <f>IF(B56="","",MONTH(B56))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M56" s="9">
         <f>IF(B56="","",YEAR(B56))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9">
         <f>IF(B57="","",ROW()-1)</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="B57" s="10" t="n">
         <v>46105</v>
@@ -4398,7 +4400,7 @@
       </c>
       <c r="J57" s="14">
         <f>IF(OR(H57="",I57=""),"",H57*I57)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
@@ -4407,17 +4409,17 @@
       </c>
       <c r="L57" s="9">
         <f>IF(B57="","",MONTH(B57))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M57" s="9">
         <f>IF(B57="","",YEAR(B57))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9">
         <f>IF(B58="","",ROW()-1)</f>
-        <v/>
+        <v>57</v>
       </c>
       <c r="B58" s="10" t="n">
         <v>46105</v>
@@ -4455,7 +4457,7 @@
       </c>
       <c r="J58" s="14">
         <f>IF(OR(H58="",I58=""),"",H58*I58)</f>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
@@ -4464,17 +4466,17 @@
       </c>
       <c r="L58" s="9">
         <f>IF(B58="","",MONTH(B58))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M58" s="9">
         <f>IF(B58="","",YEAR(B58))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9">
         <f>IF(B59="","",ROW()-1)</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="B59" s="10" t="n">
         <v>46106</v>
@@ -4512,7 +4514,7 @@
       </c>
       <c r="J59" s="14">
         <f>IF(OR(H59="",I59=""),"",H59*I59)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
@@ -4521,17 +4523,17 @@
       </c>
       <c r="L59" s="9">
         <f>IF(B59="","",MONTH(B59))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M59" s="9">
         <f>IF(B59="","",YEAR(B59))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9">
         <f>IF(B60="","",ROW()-1)</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>46106</v>
@@ -4569,7 +4571,7 @@
       </c>
       <c r="J60" s="14">
         <f>IF(OR(H60="",I60=""),"",H60*I60)</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
@@ -4578,17 +4580,17 @@
       </c>
       <c r="L60" s="9">
         <f>IF(B60="","",MONTH(B60))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M60" s="9">
         <f>IF(B60="","",YEAR(B60))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9">
         <f>IF(B61="","",ROW()-1)</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="B61" s="10" t="n">
         <v>46106</v>
@@ -4626,7 +4628,7 @@
       </c>
       <c r="J61" s="14">
         <f>IF(OR(H61="",I61=""),"",H61*I61)</f>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
@@ -4635,17 +4637,17 @@
       </c>
       <c r="L61" s="9">
         <f>IF(B61="","",MONTH(B61))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M61" s="9">
         <f>IF(B61="","",YEAR(B61))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9">
         <f>IF(B62="","",ROW()-1)</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="B62" s="10" t="n">
         <v>46107</v>
@@ -4683,7 +4685,7 @@
       </c>
       <c r="J62" s="14">
         <f>IF(OR(H62="",I62=""),"",H62*I62)</f>
-        <v/>
+        <v>-400</v>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
@@ -4692,17 +4694,17 @@
       </c>
       <c r="L62" s="9">
         <f>IF(B62="","",MONTH(B62))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M62" s="9">
         <f>IF(B62="","",YEAR(B62))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9">
         <f>IF(B63="","",ROW()-1)</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="B63" s="10" t="n">
         <v>46107</v>
@@ -4740,7 +4742,7 @@
       </c>
       <c r="J63" s="14">
         <f>IF(OR(H63="",I63=""),"",H63*I63)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
@@ -4749,17 +4751,17 @@
       </c>
       <c r="L63" s="9">
         <f>IF(B63="","",MONTH(B63))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M63" s="9">
         <f>IF(B63="","",YEAR(B63))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9">
         <f>IF(B64="","",ROW()-1)</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="B64" s="10" t="n">
         <v>46110</v>
@@ -4797,7 +4799,7 @@
       </c>
       <c r="J64" s="14">
         <f>IF(OR(H64="",I64=""),"",H64*I64)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
@@ -4806,17 +4808,17 @@
       </c>
       <c r="L64" s="9">
         <f>IF(B64="","",MONTH(B64))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M64" s="9">
         <f>IF(B64="","",YEAR(B64))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9">
         <f>IF(B65="","",ROW()-1)</f>
-        <v/>
+        <v>64</v>
       </c>
       <c r="B65" s="10" t="n">
         <v>46110</v>
@@ -4854,7 +4856,7 @@
       </c>
       <c r="J65" s="14">
         <f>IF(OR(H65="",I65=""),"",H65*I65)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
@@ -4863,17 +4865,17 @@
       </c>
       <c r="L65" s="9">
         <f>IF(B65="","",MONTH(B65))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M65" s="9">
         <f>IF(B65="","",YEAR(B65))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9">
         <f>IF(B66="","",ROW()-1)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="B66" s="10" t="n">
         <v>46110</v>
@@ -4911,7 +4913,7 @@
       </c>
       <c r="J66" s="14">
         <f>IF(OR(H66="",I66=""),"",H66*I66)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
@@ -4920,17 +4922,17 @@
       </c>
       <c r="L66" s="9">
         <f>IF(B66="","",MONTH(B66))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M66" s="9">
         <f>IF(B66="","",YEAR(B66))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9">
         <f>IF(B67="","",ROW()-1)</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="B67" s="10" t="n">
         <v>46112</v>
@@ -4968,7 +4970,7 @@
       </c>
       <c r="J67" s="14">
         <f>IF(OR(H67="",I67=""),"",H67*I67)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
@@ -4977,17 +4979,17 @@
       </c>
       <c r="L67" s="9">
         <f>IF(B67="","",MONTH(B67))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M67" s="9">
         <f>IF(B67="","",YEAR(B67))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9">
         <f>IF(B68="","",ROW()-1)</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="B68" s="10" t="n">
         <v>46113</v>
@@ -5025,7 +5027,7 @@
       </c>
       <c r="J68" s="14">
         <f>IF(OR(H68="",I68=""),"",H68*I68)</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
@@ -5034,17 +5036,17 @@
       </c>
       <c r="L68" s="9">
         <f>IF(B68="","",MONTH(B68))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M68" s="9">
         <f>IF(B68="","",YEAR(B68))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9">
         <f>IF(B69="","",ROW()-1)</f>
-        <v/>
+        <v>68</v>
       </c>
       <c r="B69" s="10" t="n">
         <v>46117</v>
@@ -5082,7 +5084,7 @@
       </c>
       <c r="J69" s="14">
         <f>IF(OR(H69="",I69=""),"",H69*I69)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
@@ -5091,17 +5093,17 @@
       </c>
       <c r="L69" s="9">
         <f>IF(B69="","",MONTH(B69))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M69" s="9">
         <f>IF(B69="","",YEAR(B69))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9">
         <f>IF(B70="","",ROW()-1)</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="B70" s="10" t="n">
         <v>46118</v>
@@ -5139,7 +5141,7 @@
       </c>
       <c r="J70" s="14">
         <f>IF(OR(H70="",I70=""),"",H70*I70)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
@@ -5148,17 +5150,17 @@
       </c>
       <c r="L70" s="9">
         <f>IF(B70="","",MONTH(B70))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M70" s="9">
         <f>IF(B70="","",YEAR(B70))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9">
         <f>IF(B71="","",ROW()-1)</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="B71" s="10" t="n">
         <v>46122</v>
@@ -5196,7 +5198,7 @@
       </c>
       <c r="J71" s="14">
         <f>IF(OR(H71="",I71=""),"",H71*I71)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
@@ -5205,17 +5207,17 @@
       </c>
       <c r="L71" s="9">
         <f>IF(B71="","",MONTH(B71))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M71" s="9">
         <f>IF(B71="","",YEAR(B71))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9">
         <f>IF(B72="","",ROW()-1)</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="B72" s="10" t="n">
         <v>46122</v>
@@ -5253,7 +5255,7 @@
       </c>
       <c r="J72" s="14">
         <f>IF(OR(H72="",I72=""),"",H72*I72)</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
@@ -5262,17 +5264,17 @@
       </c>
       <c r="L72" s="9">
         <f>IF(B72="","",MONTH(B72))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M72" s="9">
         <f>IF(B72="","",YEAR(B72))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9">
         <f>IF(B73="","",ROW()-1)</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="B73" s="10" t="n">
         <v>46123</v>
@@ -5310,7 +5312,7 @@
       </c>
       <c r="J73" s="14">
         <f>IF(OR(H73="",I73=""),"",H73*I73)</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
@@ -5319,17 +5321,17 @@
       </c>
       <c r="L73" s="9">
         <f>IF(B73="","",MONTH(B73))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M73" s="9">
         <f>IF(B73="","",YEAR(B73))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9">
         <f>IF(B74="","",ROW()-1)</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="B74" s="10" t="n">
         <v>46123</v>
@@ -5367,7 +5369,7 @@
       </c>
       <c r="J74" s="14">
         <f>IF(OR(H74="",I74=""),"",H74*I74)</f>
-        <v/>
+        <v>-800</v>
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
@@ -5376,17 +5378,17 @@
       </c>
       <c r="L74" s="9">
         <f>IF(B74="","",MONTH(B74))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M74" s="9">
         <f>IF(B74="","",YEAR(B74))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9">
         <f>IF(B75="","",ROW()-1)</f>
-        <v/>
+        <v>74</v>
       </c>
       <c r="B75" s="10" t="n">
         <v>46124</v>
@@ -5424,7 +5426,7 @@
       </c>
       <c r="J75" s="14">
         <f>IF(OR(H75="",I75=""),"",H75*I75)</f>
-        <v/>
+        <v>298</v>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
@@ -5433,17 +5435,17 @@
       </c>
       <c r="L75" s="9">
         <f>IF(B75="","",MONTH(B75))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M75" s="9">
         <f>IF(B75="","",YEAR(B75))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9">
         <f>IF(B76="","",ROW()-1)</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="B76" s="10" t="n">
         <v>46124</v>
@@ -5481,7 +5483,7 @@
       </c>
       <c r="J76" s="14">
         <f>IF(OR(H76="",I76=""),"",H76*I76)</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
@@ -5490,17 +5492,17 @@
       </c>
       <c r="L76" s="9">
         <f>IF(B76="","",MONTH(B76))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M76" s="9">
         <f>IF(B76="","",YEAR(B76))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9">
         <f>IF(B77="","",ROW()-1)</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="B77" s="10" t="n">
         <v>46124</v>
@@ -5538,7 +5540,7 @@
       </c>
       <c r="J77" s="14">
         <f>IF(OR(H77="",I77=""),"",H77*I77)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
@@ -5547,17 +5549,17 @@
       </c>
       <c r="L77" s="9">
         <f>IF(B77="","",MONTH(B77))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M77" s="9">
         <f>IF(B77="","",YEAR(B77))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9">
         <f>IF(B78="","",ROW()-1)</f>
-        <v/>
+        <v>77</v>
       </c>
       <c r="B78" s="10" t="n">
         <v>46125</v>
@@ -5595,7 +5597,7 @@
       </c>
       <c r="J78" s="14">
         <f>IF(OR(H78="",I78=""),"",H78*I78)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
@@ -5604,17 +5606,17 @@
       </c>
       <c r="L78" s="9">
         <f>IF(B78="","",MONTH(B78))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M78" s="9">
         <f>IF(B78="","",YEAR(B78))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9">
         <f>IF(B79="","",ROW()-1)</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="B79" s="10" t="n">
         <v>46126</v>
@@ -5652,7 +5654,7 @@
       </c>
       <c r="J79" s="14">
         <f>IF(OR(H79="",I79=""),"",H79*I79)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
@@ -5661,17 +5663,17 @@
       </c>
       <c r="L79" s="9">
         <f>IF(B79="","",MONTH(B79))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M79" s="9">
         <f>IF(B79="","",YEAR(B79))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9">
         <f>IF(B80="","",ROW()-1)</f>
-        <v/>
+        <v>79</v>
       </c>
       <c r="B80" s="10" t="n">
         <v>46131</v>
@@ -5709,7 +5711,7 @@
       </c>
       <c r="J80" s="14">
         <f>IF(OR(H80="",I80=""),"",H80*I80)</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
@@ -5718,17 +5720,17 @@
       </c>
       <c r="L80" s="9">
         <f>IF(B80="","",MONTH(B80))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M80" s="9">
         <f>IF(B80="","",YEAR(B80))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9">
         <f>IF(B81="","",ROW()-1)</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="B81" s="10" t="n">
         <v>46134</v>
@@ -5766,7 +5768,7 @@
       </c>
       <c r="J81" s="14">
         <f>IF(OR(H81="",I81=""),"",H81*I81)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
@@ -5775,17 +5777,17 @@
       </c>
       <c r="L81" s="9">
         <f>IF(B81="","",MONTH(B81))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M81" s="9">
         <f>IF(B81="","",YEAR(B81))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9">
         <f>IF(B82="","",ROW()-1)</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="B82" s="10" t="n">
         <v>46136</v>
@@ -5823,7 +5825,7 @@
       </c>
       <c r="J82" s="14">
         <f>IF(OR(H82="",I82=""),"",H82*I82)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
@@ -5832,17 +5834,17 @@
       </c>
       <c r="L82" s="9">
         <f>IF(B82="","",MONTH(B82))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M82" s="9">
         <f>IF(B82="","",YEAR(B82))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9">
         <f>IF(B83="","",ROW()-1)</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="B83" s="10" t="n">
         <v>46138</v>
@@ -5880,7 +5882,7 @@
       </c>
       <c r="J83" s="14">
         <f>IF(OR(H83="",I83=""),"",H83*I83)</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
@@ -5889,17 +5891,17 @@
       </c>
       <c r="L83" s="9">
         <f>IF(B83="","",MONTH(B83))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M83" s="9">
         <f>IF(B83="","",YEAR(B83))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="9">
         <f>IF(B84="","",ROW()-1)</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="B84" s="10" t="n">
         <v>46141</v>
@@ -5937,7 +5939,7 @@
       </c>
       <c r="J84" s="14">
         <f>IF(OR(H84="",I84=""),"",H84*I84)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
@@ -5946,17 +5948,17 @@
       </c>
       <c r="L84" s="9">
         <f>IF(B84="","",MONTH(B84))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M84" s="9">
         <f>IF(B84="","",YEAR(B84))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9">
         <f>IF(B85="","",ROW()-1)</f>
-        <v/>
+        <v>84</v>
       </c>
       <c r="B85" s="10" t="n">
         <v>46143</v>
@@ -5994,7 +5996,7 @@
       </c>
       <c r="J85" s="14">
         <f>IF(OR(H85="",I85=""),"",H85*I85)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
@@ -6003,17 +6005,17 @@
       </c>
       <c r="L85" s="9">
         <f>IF(B85="","",MONTH(B85))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M85" s="9">
         <f>IF(B85="","",YEAR(B85))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="9">
         <f>IF(B86="","",ROW()-1)</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="B86" s="10" t="n">
         <v>46143</v>
@@ -6051,7 +6053,7 @@
       </c>
       <c r="J86" s="14">
         <f>IF(OR(H86="",I86=""),"",H86*I86)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
@@ -6060,17 +6062,17 @@
       </c>
       <c r="L86" s="9">
         <f>IF(B86="","",MONTH(B86))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M86" s="9">
         <f>IF(B86="","",YEAR(B86))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9">
         <f>IF(B87="","",ROW()-1)</f>
-        <v/>
+        <v>86</v>
       </c>
       <c r="B87" s="10" t="n">
         <v>46146</v>
@@ -6108,7 +6110,7 @@
       </c>
       <c r="J87" s="14">
         <f>IF(OR(H87="",I87=""),"",H87*I87)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
@@ -6117,17 +6119,17 @@
       </c>
       <c r="L87" s="9">
         <f>IF(B87="","",MONTH(B87))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M87" s="9">
         <f>IF(B87="","",YEAR(B87))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9">
         <f>IF(B88="","",ROW()-1)</f>
-        <v/>
+        <v>87</v>
       </c>
       <c r="B88" s="10" t="n">
         <v>46148</v>
@@ -6165,7 +6167,7 @@
       </c>
       <c r="J88" s="14">
         <f>IF(OR(H88="",I88=""),"",H88*I88)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
@@ -6174,17 +6176,17 @@
       </c>
       <c r="L88" s="9">
         <f>IF(B88="","",MONTH(B88))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M88" s="9">
         <f>IF(B88="","",YEAR(B88))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9">
         <f>IF(B89="","",ROW()-1)</f>
-        <v/>
+        <v>88</v>
       </c>
       <c r="B89" s="10" t="n">
         <v>46149</v>
@@ -6222,7 +6224,7 @@
       </c>
       <c r="J89" s="14">
         <f>IF(OR(H89="",I89=""),"",H89*I89)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
@@ -6231,17 +6233,17 @@
       </c>
       <c r="L89" s="9">
         <f>IF(B89="","",MONTH(B89))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M89" s="9">
         <f>IF(B89="","",YEAR(B89))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9">
         <f>IF(B90="","",ROW()-1)</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="B90" s="10" t="n">
         <v>46150</v>
@@ -6279,7 +6281,7 @@
       </c>
       <c r="J90" s="14">
         <f>IF(OR(H90="",I90=""),"",H90*I90)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
@@ -6288,17 +6290,17 @@
       </c>
       <c r="L90" s="9">
         <f>IF(B90="","",MONTH(B90))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M90" s="9">
         <f>IF(B90="","",YEAR(B90))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9">
         <f>IF(B91="","",ROW()-1)</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="B91" s="10" t="n">
         <v>46152</v>
@@ -6336,7 +6338,7 @@
       </c>
       <c r="J91" s="14">
         <f>IF(OR(H91="",I91=""),"",H91*I91)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
@@ -6345,17 +6347,17 @@
       </c>
       <c r="L91" s="9">
         <f>IF(B91="","",MONTH(B91))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M91" s="9">
         <f>IF(B91="","",YEAR(B91))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="9">
         <f>IF(B92="","",ROW()-1)</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="B92" s="10" t="n">
         <v>46153</v>
@@ -6393,7 +6395,7 @@
       </c>
       <c r="J92" s="14">
         <f>IF(OR(H92="",I92=""),"",H92*I92)</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
@@ -6402,17 +6404,17 @@
       </c>
       <c r="L92" s="9">
         <f>IF(B92="","",MONTH(B92))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M92" s="9">
         <f>IF(B92="","",YEAR(B92))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="9">
         <f>IF(B93="","",ROW()-1)</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="B93" s="10" t="n">
         <v>46161</v>
@@ -6450,7 +6452,7 @@
       </c>
       <c r="J93" s="14">
         <f>IF(OR(H93="",I93=""),"",H93*I93)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
@@ -6459,17 +6461,17 @@
       </c>
       <c r="L93" s="9">
         <f>IF(B93="","",MONTH(B93))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M93" s="9">
         <f>IF(B93="","",YEAR(B93))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9">
         <f>IF(B94="","",ROW()-1)</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="B94" s="10" t="n">
         <v>46166</v>
@@ -6507,7 +6509,7 @@
       </c>
       <c r="J94" s="14">
         <f>IF(OR(H94="",I94=""),"",H94*I94)</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
@@ -6516,17 +6518,17 @@
       </c>
       <c r="L94" s="9">
         <f>IF(B94="","",MONTH(B94))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M94" s="9">
         <f>IF(B94="","",YEAR(B94))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="9">
         <f>IF(B95="","",ROW()-1)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="B95" s="10" t="n">
         <v>46168</v>
@@ -6564,7 +6566,7 @@
       </c>
       <c r="J95" s="14">
         <f>IF(OR(H95="",I95=""),"",H95*I95)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
@@ -6573,17 +6575,17 @@
       </c>
       <c r="L95" s="9">
         <f>IF(B95="","",MONTH(B95))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M95" s="9">
         <f>IF(B95="","",YEAR(B95))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9">
         <f>IF(B96="","",ROW()-1)</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="B96" s="10" t="n">
         <v>46169</v>
@@ -6621,7 +6623,7 @@
       </c>
       <c r="J96" s="14">
         <f>IF(OR(H96="",I96=""),"",H96*I96)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
@@ -6630,17 +6632,17 @@
       </c>
       <c r="L96" s="9">
         <f>IF(B96="","",MONTH(B96))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M96" s="9">
         <f>IF(B96="","",YEAR(B96))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9">
         <f>IF(B97="","",ROW()-1)</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="B97" s="10" t="n">
         <v>46169</v>
@@ -6678,7 +6680,7 @@
       </c>
       <c r="J97" s="14">
         <f>IF(OR(H97="",I97=""),"",H97*I97)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
@@ -6687,17 +6689,17 @@
       </c>
       <c r="L97" s="9">
         <f>IF(B97="","",MONTH(B97))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M97" s="9">
         <f>IF(B97="","",YEAR(B97))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9">
         <f>IF(B98="","",ROW()-1)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="B98" s="10" t="n">
         <v>46169</v>
@@ -6735,7 +6737,7 @@
       </c>
       <c r="J98" s="14">
         <f>IF(OR(H98="",I98=""),"",H98*I98)</f>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
@@ -6744,17 +6746,17 @@
       </c>
       <c r="L98" s="9">
         <f>IF(B98="","",MONTH(B98))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M98" s="9">
         <f>IF(B98="","",YEAR(B98))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9">
         <f>IF(B99="","",ROW()-1)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="B99" s="10" t="n">
         <v>46171</v>
@@ -6792,7 +6794,7 @@
       </c>
       <c r="J99" s="14">
         <f>IF(OR(H99="",I99=""),"",H99*I99)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
@@ -6801,17 +6803,17 @@
       </c>
       <c r="L99" s="9">
         <f>IF(B99="","",MONTH(B99))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M99" s="9">
         <f>IF(B99="","",YEAR(B99))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9">
         <f>IF(B100="","",ROW()-1)</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="B100" s="10" t="n">
         <v>46173</v>
@@ -6849,7 +6851,7 @@
       </c>
       <c r="J100" s="14">
         <f>IF(OR(H100="",I100=""),"",H100*I100)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
@@ -6858,17 +6860,17 @@
       </c>
       <c r="L100" s="9">
         <f>IF(B100="","",MONTH(B100))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M100" s="9">
         <f>IF(B100="","",YEAR(B100))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9">
         <f>IF(B101="","",ROW()-1)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="B101" s="10" t="n">
         <v>46173</v>
@@ -6906,7 +6908,7 @@
       </c>
       <c r="J101" s="14">
         <f>IF(OR(H101="",I101=""),"",H101*I101)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
@@ -6915,17 +6917,17 @@
       </c>
       <c r="L101" s="9">
         <f>IF(B101="","",MONTH(B101))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M101" s="9">
         <f>IF(B101="","",YEAR(B101))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9">
         <f>IF(B102="","",ROW()-1)</f>
-        <v/>
+        <v>101</v>
       </c>
       <c r="B102" s="10" t="n">
         <v>46175</v>
@@ -6963,7 +6965,7 @@
       </c>
       <c r="J102" s="14">
         <f>IF(OR(H102="",I102=""),"",H102*I102)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
@@ -6972,17 +6974,17 @@
       </c>
       <c r="L102" s="9">
         <f>IF(B102="","",MONTH(B102))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M102" s="9">
         <f>IF(B102="","",YEAR(B102))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9">
         <f>IF(B103="","",ROW()-1)</f>
-        <v/>
+        <v>102</v>
       </c>
       <c r="B103" s="10" t="n">
         <v>46177</v>
@@ -7020,7 +7022,7 @@
       </c>
       <c r="J103" s="14">
         <f>IF(OR(H103="",I103=""),"",H103*I103)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
@@ -7029,17 +7031,17 @@
       </c>
       <c r="L103" s="9">
         <f>IF(B103="","",MONTH(B103))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M103" s="9">
         <f>IF(B103="","",YEAR(B103))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9">
         <f>IF(B104="","",ROW()-1)</f>
-        <v/>
+        <v>103</v>
       </c>
       <c r="B104" s="10" t="n">
         <v>46181</v>
@@ -7077,7 +7079,7 @@
       </c>
       <c r="J104" s="14">
         <f>IF(OR(H104="",I104=""),"",H104*I104)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
@@ -7086,17 +7088,17 @@
       </c>
       <c r="L104" s="9">
         <f>IF(B104="","",MONTH(B104))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M104" s="9">
         <f>IF(B104="","",YEAR(B104))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9">
         <f>IF(B105="","",ROW()-1)</f>
-        <v/>
+        <v>104</v>
       </c>
       <c r="B105" s="10" t="n">
         <v>46181</v>
@@ -7134,7 +7136,7 @@
       </c>
       <c r="J105" s="14">
         <f>IF(OR(H105="",I105=""),"",H105*I105)</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
@@ -7143,17 +7145,17 @@
       </c>
       <c r="L105" s="9">
         <f>IF(B105="","",MONTH(B105))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M105" s="9">
         <f>IF(B105="","",YEAR(B105))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="9">
         <f>IF(B106="","",ROW()-1)</f>
-        <v/>
+        <v>105</v>
       </c>
       <c r="B106" s="10" t="n">
         <v>46182</v>
@@ -7191,7 +7193,7 @@
       </c>
       <c r="J106" s="14">
         <f>IF(OR(H106="",I106=""),"",H106*I106)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
@@ -7200,17 +7202,17 @@
       </c>
       <c r="L106" s="9">
         <f>IF(B106="","",MONTH(B106))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M106" s="9">
         <f>IF(B106="","",YEAR(B106))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="9">
         <f>IF(B107="","",ROW()-1)</f>
-        <v/>
+        <v>106</v>
       </c>
       <c r="B107" s="10" t="n">
         <v>46183</v>
@@ -7248,7 +7250,7 @@
       </c>
       <c r="J107" s="14">
         <f>IF(OR(H107="",I107=""),"",H107*I107)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
@@ -7257,17 +7259,17 @@
       </c>
       <c r="L107" s="9">
         <f>IF(B107="","",MONTH(B107))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M107" s="9">
         <f>IF(B107="","",YEAR(B107))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9">
         <f>IF(B108="","",ROW()-1)</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="B108" s="10" t="n">
         <v>46186</v>
@@ -7305,7 +7307,7 @@
       </c>
       <c r="J108" s="14">
         <f>IF(OR(H108="",I108=""),"",H108*I108)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
@@ -7314,17 +7316,17 @@
       </c>
       <c r="L108" s="9">
         <f>IF(B108="","",MONTH(B108))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M108" s="9">
         <f>IF(B108="","",YEAR(B108))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9">
         <f>IF(B109="","",ROW()-1)</f>
-        <v/>
+        <v>108</v>
       </c>
       <c r="B109" s="10" t="n">
         <v>46188</v>
@@ -7362,7 +7364,7 @@
       </c>
       <c r="J109" s="14">
         <f>IF(OR(H109="",I109=""),"",H109*I109)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
@@ -7371,17 +7373,17 @@
       </c>
       <c r="L109" s="9">
         <f>IF(B109="","",MONTH(B109))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M109" s="9">
         <f>IF(B109="","",YEAR(B109))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9">
         <f>IF(B110="","",ROW()-1)</f>
-        <v/>
+        <v>109</v>
       </c>
       <c r="B110" s="10" t="n">
         <v>46188</v>
@@ -7419,7 +7421,7 @@
       </c>
       <c r="J110" s="14">
         <f>IF(OR(H110="",I110=""),"",H110*I110)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
@@ -7428,17 +7430,17 @@
       </c>
       <c r="L110" s="9">
         <f>IF(B110="","",MONTH(B110))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M110" s="9">
         <f>IF(B110="","",YEAR(B110))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9">
         <f>IF(B111="","",ROW()-1)</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="B111" s="10" t="n">
         <v>46188</v>
@@ -7476,7 +7478,7 @@
       </c>
       <c r="J111" s="14">
         <f>IF(OR(H111="",I111=""),"",H111*I111)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
@@ -7485,17 +7487,17 @@
       </c>
       <c r="L111" s="9">
         <f>IF(B111="","",MONTH(B111))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M111" s="9">
         <f>IF(B111="","",YEAR(B111))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="9">
         <f>IF(B112="","",ROW()-1)</f>
-        <v/>
+        <v>111</v>
       </c>
       <c r="B112" s="10" t="n">
         <v>46188</v>
@@ -7533,7 +7535,7 @@
       </c>
       <c r="J112" s="14">
         <f>IF(OR(H112="",I112=""),"",H112*I112)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
@@ -7542,17 +7544,17 @@
       </c>
       <c r="L112" s="9">
         <f>IF(B112="","",MONTH(B112))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M112" s="9">
         <f>IF(B112="","",YEAR(B112))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9">
         <f>IF(B113="","",ROW()-1)</f>
-        <v/>
+        <v>112</v>
       </c>
       <c r="B113" s="10" t="n">
         <v>46189</v>
@@ -7590,7 +7592,7 @@
       </c>
       <c r="J113" s="14">
         <f>IF(OR(H113="",I113=""),"",H113*I113)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
@@ -7599,17 +7601,17 @@
       </c>
       <c r="L113" s="9">
         <f>IF(B113="","",MONTH(B113))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M113" s="9">
         <f>IF(B113="","",YEAR(B113))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9">
         <f>IF(B114="","",ROW()-1)</f>
-        <v/>
+        <v>113</v>
       </c>
       <c r="B114" s="10" t="n">
         <v>46189</v>
@@ -7647,7 +7649,7 @@
       </c>
       <c r="J114" s="14">
         <f>IF(OR(H114="",I114=""),"",H114*I114)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
@@ -7656,17 +7658,17 @@
       </c>
       <c r="L114" s="9">
         <f>IF(B114="","",MONTH(B114))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M114" s="9">
         <f>IF(B114="","",YEAR(B114))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9">
         <f>IF(B115="","",ROW()-1)</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="B115" s="10" t="n">
         <v>46191</v>
@@ -7704,7 +7706,7 @@
       </c>
       <c r="J115" s="14">
         <f>IF(OR(H115="",I115=""),"",H115*I115)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
@@ -7713,17 +7715,17 @@
       </c>
       <c r="L115" s="9">
         <f>IF(B115="","",MONTH(B115))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M115" s="9">
         <f>IF(B115="","",YEAR(B115))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9">
         <f>IF(B116="","",ROW()-1)</f>
-        <v/>
+        <v>115</v>
       </c>
       <c r="B116" s="10" t="n">
         <v>46192</v>
@@ -7761,7 +7763,7 @@
       </c>
       <c r="J116" s="14">
         <f>IF(OR(H116="",I116=""),"",H116*I116)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
@@ -7770,17 +7772,17 @@
       </c>
       <c r="L116" s="9">
         <f>IF(B116="","",MONTH(B116))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M116" s="9">
         <f>IF(B116="","",YEAR(B116))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9">
         <f>IF(B117="","",ROW()-1)</f>
-        <v/>
+        <v>116</v>
       </c>
       <c r="B117" s="10" t="n">
         <v>46192</v>
@@ -7818,7 +7820,7 @@
       </c>
       <c r="J117" s="14">
         <f>IF(OR(H117="",I117=""),"",H117*I117)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
@@ -7827,17 +7829,17 @@
       </c>
       <c r="L117" s="9">
         <f>IF(B117="","",MONTH(B117))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M117" s="9">
         <f>IF(B117="","",YEAR(B117))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="9">
         <f>IF(B118="","",ROW()-1)</f>
-        <v/>
+        <v>117</v>
       </c>
       <c r="B118" s="10" t="n">
         <v>46195</v>
@@ -7875,7 +7877,7 @@
       </c>
       <c r="J118" s="14">
         <f>IF(OR(H118="",I118=""),"",H118*I118)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
@@ -7884,17 +7886,17 @@
       </c>
       <c r="L118" s="9">
         <f>IF(B118="","",MONTH(B118))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M118" s="9">
         <f>IF(B118="","",YEAR(B118))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="9">
         <f>IF(B119="","",ROW()-1)</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="B119" s="10" t="n">
         <v>46200</v>
@@ -7932,7 +7934,7 @@
       </c>
       <c r="J119" s="14">
         <f>IF(OR(H119="",I119=""),"",H119*I119)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
@@ -7941,17 +7943,17 @@
       </c>
       <c r="L119" s="9">
         <f>IF(B119="","",MONTH(B119))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M119" s="9">
         <f>IF(B119="","",YEAR(B119))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="9">
         <f>IF(B120="","",ROW()-1)</f>
-        <v/>
+        <v>119</v>
       </c>
       <c r="B120" s="10" t="n">
         <v>46202</v>
@@ -7989,7 +7991,7 @@
       </c>
       <c r="J120" s="14">
         <f>IF(OR(H120="",I120=""),"",H120*I120)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
@@ -7998,17 +8000,17 @@
       </c>
       <c r="L120" s="9">
         <f>IF(B120="","",MONTH(B120))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M120" s="9">
         <f>IF(B120="","",YEAR(B120))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9">
         <f>IF(B121="","",ROW()-1)</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="B121" s="10" t="n">
         <v>46203</v>
@@ -8046,7 +8048,7 @@
       </c>
       <c r="J121" s="14">
         <f>IF(OR(H121="",I121=""),"",H121*I121)</f>
-        <v/>
+        <v>298</v>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
@@ -8055,17 +8057,17 @@
       </c>
       <c r="L121" s="9">
         <f>IF(B121="","",MONTH(B121))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M121" s="9">
         <f>IF(B121="","",YEAR(B121))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9">
         <f>IF(B122="","",ROW()-1)</f>
-        <v/>
+        <v>121</v>
       </c>
       <c r="B122" s="10" t="n">
         <v>46203</v>
@@ -8103,7 +8105,7 @@
       </c>
       <c r="J122" s="14">
         <f>IF(OR(H122="",I122=""),"",H122*I122)</f>
-        <v/>
+        <v>-300</v>
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
@@ -8112,17 +8114,17 @@
       </c>
       <c r="L122" s="9">
         <f>IF(B122="","",MONTH(B122))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M122" s="9">
         <f>IF(B122="","",YEAR(B122))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9">
         <f>IF(B123="","",ROW()-1)</f>
-        <v/>
+        <v>122</v>
       </c>
       <c r="B123" s="10" t="n">
         <v>46204</v>
@@ -8160,7 +8162,7 @@
       </c>
       <c r="J123" s="14">
         <f>IF(OR(H123="",I123=""),"",H123*I123)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
@@ -8169,17 +8171,17 @@
       </c>
       <c r="L123" s="9">
         <f>IF(B123="","",MONTH(B123))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M123" s="9">
         <f>IF(B123="","",YEAR(B123))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9">
         <f>IF(B124="","",ROW()-1)</f>
-        <v/>
+        <v>123</v>
       </c>
       <c r="B124" s="10" t="n">
         <v>46204</v>
@@ -8217,7 +8219,7 @@
       </c>
       <c r="J124" s="14">
         <f>IF(OR(H124="",I124=""),"",H124*I124)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K124" s="11" t="inlineStr">
         <is>
@@ -8226,17 +8228,17 @@
       </c>
       <c r="L124" s="9">
         <f>IF(B124="","",MONTH(B124))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M124" s="9">
         <f>IF(B124="","",YEAR(B124))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9">
         <f>IF(B125="","",ROW()-1)</f>
-        <v/>
+        <v>124</v>
       </c>
       <c r="B125" s="10" t="n">
         <v>46205</v>
@@ -8274,7 +8276,7 @@
       </c>
       <c r="J125" s="14">
         <f>IF(OR(H125="",I125=""),"",H125*I125)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
@@ -8283,17 +8285,17 @@
       </c>
       <c r="L125" s="9">
         <f>IF(B125="","",MONTH(B125))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M125" s="9">
         <f>IF(B125="","",YEAR(B125))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9">
         <f>IF(B126="","",ROW()-1)</f>
-        <v/>
+        <v>125</v>
       </c>
       <c r="B126" s="10" t="n">
         <v>46205</v>
@@ -8331,7 +8333,7 @@
       </c>
       <c r="J126" s="14">
         <f>IF(OR(H126="",I126=""),"",H126*I126)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
@@ -8340,17 +8342,17 @@
       </c>
       <c r="L126" s="9">
         <f>IF(B126="","",MONTH(B126))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M126" s="9">
         <f>IF(B126="","",YEAR(B126))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="9">
         <f>IF(B127="","",ROW()-1)</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="B127" s="10" t="n">
         <v>46207</v>
@@ -8388,7 +8390,7 @@
       </c>
       <c r="J127" s="14">
         <f>IF(OR(H127="",I127=""),"",H127*I127)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
@@ -8397,17 +8399,17 @@
       </c>
       <c r="L127" s="9">
         <f>IF(B127="","",MONTH(B127))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M127" s="9">
         <f>IF(B127="","",YEAR(B127))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="9">
         <f>IF(B128="","",ROW()-1)</f>
-        <v/>
+        <v>127</v>
       </c>
       <c r="B128" s="10" t="n">
         <v>46208</v>
@@ -8445,7 +8447,7 @@
       </c>
       <c r="J128" s="14">
         <f>IF(OR(H128="",I128=""),"",H128*I128)</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="K128" s="11" t="inlineStr">
         <is>
@@ -8454,17 +8456,17 @@
       </c>
       <c r="L128" s="9">
         <f>IF(B128="","",MONTH(B128))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M128" s="9">
         <f>IF(B128="","",YEAR(B128))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9">
         <f>IF(B129="","",ROW()-1)</f>
-        <v/>
+        <v>128</v>
       </c>
       <c r="B129" s="10" t="n">
         <v>46214</v>
@@ -8502,7 +8504,7 @@
       </c>
       <c r="J129" s="14">
         <f>IF(OR(H129="",I129=""),"",H129*I129)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
@@ -8511,17 +8513,17 @@
       </c>
       <c r="L129" s="9">
         <f>IF(B129="","",MONTH(B129))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M129" s="9">
         <f>IF(B129="","",YEAR(B129))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9">
         <f>IF(B130="","",ROW()-1)</f>
-        <v/>
+        <v>129</v>
       </c>
       <c r="B130" s="10" t="n">
         <v>46215</v>
@@ -8559,7 +8561,7 @@
       </c>
       <c r="J130" s="14">
         <f>IF(OR(H130="",I130=""),"",H130*I130)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K130" s="11" t="inlineStr">
         <is>
@@ -8568,17 +8570,17 @@
       </c>
       <c r="L130" s="9">
         <f>IF(B130="","",MONTH(B130))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M130" s="9">
         <f>IF(B130="","",YEAR(B130))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9">
         <f>IF(B131="","",ROW()-1)</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="B131" s="10" t="n">
         <v>46215</v>
@@ -8616,7 +8618,7 @@
       </c>
       <c r="J131" s="14">
         <f>IF(OR(H131="",I131=""),"",H131*I131)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
@@ -8625,17 +8627,17 @@
       </c>
       <c r="L131" s="9">
         <f>IF(B131="","",MONTH(B131))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M131" s="9">
         <f>IF(B131="","",YEAR(B131))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9">
         <f>IF(B132="","",ROW()-1)</f>
-        <v/>
+        <v>131</v>
       </c>
       <c r="B132" s="10" t="n">
         <v>46217</v>
@@ -8673,7 +8675,7 @@
       </c>
       <c r="J132" s="14">
         <f>IF(OR(H132="",I132=""),"",H132*I132)</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="K132" s="11" t="inlineStr">
         <is>
@@ -8682,17 +8684,17 @@
       </c>
       <c r="L132" s="9">
         <f>IF(B132="","",MONTH(B132))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M132" s="9">
         <f>IF(B132="","",YEAR(B132))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9">
         <f>IF(B133="","",ROW()-1)</f>
-        <v/>
+        <v>132</v>
       </c>
       <c r="B133" s="10" t="n">
         <v>46217</v>
@@ -8730,7 +8732,7 @@
       </c>
       <c r="J133" s="14">
         <f>IF(OR(H133="",I133=""),"",H133*I133)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
@@ -8739,17 +8741,17 @@
       </c>
       <c r="L133" s="9">
         <f>IF(B133="","",MONTH(B133))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M133" s="9">
         <f>IF(B133="","",YEAR(B133))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="9">
         <f>IF(B134="","",ROW()-1)</f>
-        <v/>
+        <v>133</v>
       </c>
       <c r="B134" s="10" t="n">
         <v>46218</v>
@@ -8787,7 +8789,7 @@
       </c>
       <c r="J134" s="14">
         <f>IF(OR(H134="",I134=""),"",H134*I134)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
@@ -8796,17 +8798,17 @@
       </c>
       <c r="L134" s="9">
         <f>IF(B134="","",MONTH(B134))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M134" s="9">
         <f>IF(B134="","",YEAR(B134))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9">
         <f>IF(B135="","",ROW()-1)</f>
-        <v/>
+        <v>134</v>
       </c>
       <c r="B135" s="10" t="n">
         <v>46219</v>
@@ -8844,7 +8846,7 @@
       </c>
       <c r="J135" s="14">
         <f>IF(OR(H135="",I135=""),"",H135*I135)</f>
-        <v/>
+        <v>7200</v>
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
@@ -8853,17 +8855,17 @@
       </c>
       <c r="L135" s="9">
         <f>IF(B135="","",MONTH(B135))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M135" s="9">
         <f>IF(B135="","",YEAR(B135))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="9">
         <f>IF(B136="","",ROW()-1)</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="B136" s="10" t="n">
         <v>46219</v>
@@ -8901,7 +8903,7 @@
       </c>
       <c r="J136" s="14">
         <f>IF(OR(H136="",I136=""),"",H136*I136)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
@@ -8910,17 +8912,17 @@
       </c>
       <c r="L136" s="9">
         <f>IF(B136="","",MONTH(B136))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M136" s="9">
         <f>IF(B136="","",YEAR(B136))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="9">
         <f>IF(B137="","",ROW()-1)</f>
-        <v/>
+        <v>136</v>
       </c>
       <c r="B137" s="10" t="n">
         <v>46221</v>
@@ -8958,7 +8960,7 @@
       </c>
       <c r="J137" s="14">
         <f>IF(OR(H137="",I137=""),"",H137*I137)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
@@ -8967,17 +8969,17 @@
       </c>
       <c r="L137" s="9">
         <f>IF(B137="","",MONTH(B137))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M137" s="9">
         <f>IF(B137="","",YEAR(B137))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="9">
         <f>IF(B138="","",ROW()-1)</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="B138" s="10" t="n">
         <v>46222</v>
@@ -9015,7 +9017,7 @@
       </c>
       <c r="J138" s="14">
         <f>IF(OR(H138="",I138=""),"",H138*I138)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
@@ -9024,17 +9026,17 @@
       </c>
       <c r="L138" s="9">
         <f>IF(B138="","",MONTH(B138))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M138" s="9">
         <f>IF(B138="","",YEAR(B138))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="9">
         <f>IF(B139="","",ROW()-1)</f>
-        <v/>
+        <v>138</v>
       </c>
       <c r="B139" s="10" t="n">
         <v>46222</v>
@@ -9072,7 +9074,7 @@
       </c>
       <c r="J139" s="14">
         <f>IF(OR(H139="",I139=""),"",H139*I139)</f>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
@@ -9081,17 +9083,17 @@
       </c>
       <c r="L139" s="9">
         <f>IF(B139="","",MONTH(B139))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M139" s="9">
         <f>IF(B139="","",YEAR(B139))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="9">
         <f>IF(B140="","",ROW()-1)</f>
-        <v/>
+        <v>139</v>
       </c>
       <c r="B140" s="10" t="n">
         <v>46225</v>
@@ -9129,7 +9131,7 @@
       </c>
       <c r="J140" s="14">
         <f>IF(OR(H140="",I140=""),"",H140*I140)</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="K140" s="11" t="inlineStr">
         <is>
@@ -9138,17 +9140,17 @@
       </c>
       <c r="L140" s="9">
         <f>IF(B140="","",MONTH(B140))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M140" s="9">
         <f>IF(B140="","",YEAR(B140))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="9">
         <f>IF(B141="","",ROW()-1)</f>
-        <v/>
+        <v>140</v>
       </c>
       <c r="B141" s="10" t="n">
         <v>46227</v>
@@ -9186,7 +9188,7 @@
       </c>
       <c r="J141" s="14">
         <f>IF(OR(H141="",I141=""),"",H141*I141)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K141" s="11" t="inlineStr">
         <is>
@@ -9195,17 +9197,17 @@
       </c>
       <c r="L141" s="9">
         <f>IF(B141="","",MONTH(B141))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M141" s="9">
         <f>IF(B141="","",YEAR(B141))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="9">
         <f>IF(B142="","",ROW()-1)</f>
-        <v/>
+        <v>141</v>
       </c>
       <c r="B142" s="10" t="n">
         <v>46228</v>
@@ -9243,7 +9245,7 @@
       </c>
       <c r="J142" s="14">
         <f>IF(OR(H142="",I142=""),"",H142*I142)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K142" s="11" t="inlineStr">
         <is>
@@ -9252,17 +9254,17 @@
       </c>
       <c r="L142" s="9">
         <f>IF(B142="","",MONTH(B142))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M142" s="9">
         <f>IF(B142="","",YEAR(B142))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9">
         <f>IF(B143="","",ROW()-1)</f>
-        <v/>
+        <v>142</v>
       </c>
       <c r="B143" s="10" t="n">
         <v>46233</v>
@@ -9300,7 +9302,7 @@
       </c>
       <c r="J143" s="14">
         <f>IF(OR(H143="",I143=""),"",H143*I143)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K143" s="11" t="inlineStr">
         <is>
@@ -9309,17 +9311,17 @@
       </c>
       <c r="L143" s="9">
         <f>IF(B143="","",MONTH(B143))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M143" s="9">
         <f>IF(B143="","",YEAR(B143))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="9">
         <f>IF(B144="","",ROW()-1)</f>
-        <v/>
+        <v>143</v>
       </c>
       <c r="B144" s="10" t="n">
         <v>46233</v>
@@ -9357,7 +9359,7 @@
       </c>
       <c r="J144" s="14">
         <f>IF(OR(H144="",I144=""),"",H144*I144)</f>
-        <v/>
+        <v>-300</v>
       </c>
       <c r="K144" s="11" t="inlineStr">
         <is>
@@ -9366,17 +9368,17 @@
       </c>
       <c r="L144" s="9">
         <f>IF(B144="","",MONTH(B144))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M144" s="9">
         <f>IF(B144="","",YEAR(B144))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="9">
         <f>IF(B145="","",ROW()-1)</f>
-        <v/>
+        <v>144</v>
       </c>
       <c r="B145" s="10" t="n">
         <v>46234</v>
@@ -9414,7 +9416,7 @@
       </c>
       <c r="J145" s="14">
         <f>IF(OR(H145="",I145=""),"",H145*I145)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K145" s="11" t="inlineStr">
         <is>
@@ -9423,17 +9425,17 @@
       </c>
       <c r="L145" s="9">
         <f>IF(B145="","",MONTH(B145))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M145" s="9">
         <f>IF(B145="","",YEAR(B145))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="9">
         <f>IF(B146="","",ROW()-1)</f>
-        <v/>
+        <v>145</v>
       </c>
       <c r="B146" s="10" t="n">
         <v>46235</v>
@@ -9471,7 +9473,7 @@
       </c>
       <c r="J146" s="14">
         <f>IF(OR(H146="",I146=""),"",H146*I146)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K146" s="11" t="inlineStr">
         <is>
@@ -9480,17 +9482,17 @@
       </c>
       <c r="L146" s="9">
         <f>IF(B146="","",MONTH(B146))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M146" s="9">
         <f>IF(B146="","",YEAR(B146))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="9">
         <f>IF(B147="","",ROW()-1)</f>
-        <v/>
+        <v>146</v>
       </c>
       <c r="B147" s="10" t="n">
         <v>46235</v>
@@ -9528,7 +9530,7 @@
       </c>
       <c r="J147" s="14">
         <f>IF(OR(H147="",I147=""),"",H147*I147)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K147" s="11" t="inlineStr">
         <is>
@@ -9537,17 +9539,17 @@
       </c>
       <c r="L147" s="9">
         <f>IF(B147="","",MONTH(B147))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M147" s="9">
         <f>IF(B147="","",YEAR(B147))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="9">
         <f>IF(B148="","",ROW()-1)</f>
-        <v/>
+        <v>147</v>
       </c>
       <c r="B148" s="10" t="n">
         <v>46236</v>
@@ -9585,7 +9587,7 @@
       </c>
       <c r="J148" s="14">
         <f>IF(OR(H148="",I148=""),"",H148*I148)</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="K148" s="11" t="inlineStr">
         <is>
@@ -9594,17 +9596,17 @@
       </c>
       <c r="L148" s="9">
         <f>IF(B148="","",MONTH(B148))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M148" s="9">
         <f>IF(B148="","",YEAR(B148))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="9">
         <f>IF(B149="","",ROW()-1)</f>
-        <v/>
+        <v>148</v>
       </c>
       <c r="B149" s="10" t="n">
         <v>46236</v>
@@ -9642,7 +9644,7 @@
       </c>
       <c r="J149" s="14">
         <f>IF(OR(H149="",I149=""),"",H149*I149)</f>
-        <v/>
+        <v>447</v>
       </c>
       <c r="K149" s="11" t="inlineStr">
         <is>
@@ -9651,17 +9653,17 @@
       </c>
       <c r="L149" s="9">
         <f>IF(B149="","",MONTH(B149))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M149" s="9">
         <f>IF(B149="","",YEAR(B149))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="9">
         <f>IF(B150="","",ROW()-1)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="B150" s="10" t="n">
         <v>46237</v>
@@ -9699,7 +9701,7 @@
       </c>
       <c r="J150" s="14">
         <f>IF(OR(H150="",I150=""),"",H150*I150)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K150" s="11" t="inlineStr">
         <is>
@@ -9708,17 +9710,17 @@
       </c>
       <c r="L150" s="9">
         <f>IF(B150="","",MONTH(B150))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M150" s="9">
         <f>IF(B150="","",YEAR(B150))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="9">
         <f>IF(B151="","",ROW()-1)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="B151" s="10" t="n">
         <v>46237</v>
@@ -9756,7 +9758,7 @@
       </c>
       <c r="J151" s="14">
         <f>IF(OR(H151="",I151=""),"",H151*I151)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K151" s="11" t="inlineStr">
         <is>
@@ -9765,17 +9767,17 @@
       </c>
       <c r="L151" s="9">
         <f>IF(B151="","",MONTH(B151))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M151" s="9">
         <f>IF(B151="","",YEAR(B151))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="9">
         <f>IF(B152="","",ROW()-1)</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="B152" s="10" t="n">
         <v>46238</v>
@@ -9813,7 +9815,7 @@
       </c>
       <c r="J152" s="14">
         <f>IF(OR(H152="",I152=""),"",H152*I152)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K152" s="11" t="inlineStr">
         <is>
@@ -9822,17 +9824,17 @@
       </c>
       <c r="L152" s="9">
         <f>IF(B152="","",MONTH(B152))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M152" s="9">
         <f>IF(B152="","",YEAR(B152))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="9">
         <f>IF(B153="","",ROW()-1)</f>
-        <v/>
+        <v>152</v>
       </c>
       <c r="B153" s="10" t="n">
         <v>46239</v>
@@ -9870,7 +9872,7 @@
       </c>
       <c r="J153" s="14">
         <f>IF(OR(H153="",I153=""),"",H153*I153)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K153" s="11" t="inlineStr">
         <is>
@@ -9879,17 +9881,17 @@
       </c>
       <c r="L153" s="9">
         <f>IF(B153="","",MONTH(B153))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M153" s="9">
         <f>IF(B153="","",YEAR(B153))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="9">
         <f>IF(B154="","",ROW()-1)</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="B154" s="10" t="n">
         <v>46239</v>
@@ -9927,7 +9929,7 @@
       </c>
       <c r="J154" s="14">
         <f>IF(OR(H154="",I154=""),"",H154*I154)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="K154" s="11" t="inlineStr">
         <is>
@@ -9936,17 +9938,17 @@
       </c>
       <c r="L154" s="9">
         <f>IF(B154="","",MONTH(B154))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M154" s="9">
         <f>IF(B154="","",YEAR(B154))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="9">
         <f>IF(B155="","",ROW()-1)</f>
-        <v/>
+        <v>154</v>
       </c>
       <c r="B155" s="10" t="n">
         <v>46240</v>
@@ -9984,7 +9986,7 @@
       </c>
       <c r="J155" s="14">
         <f>IF(OR(H155="",I155=""),"",H155*I155)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K155" s="11" t="inlineStr">
         <is>
@@ -9993,17 +9995,17 @@
       </c>
       <c r="L155" s="9">
         <f>IF(B155="","",MONTH(B155))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M155" s="9">
         <f>IF(B155="","",YEAR(B155))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="9">
         <f>IF(B156="","",ROW()-1)</f>
-        <v/>
+        <v>155</v>
       </c>
       <c r="B156" s="10" t="n">
         <v>46240</v>
@@ -10041,7 +10043,7 @@
       </c>
       <c r="J156" s="14">
         <f>IF(OR(H156="",I156=""),"",H156*I156)</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="K156" s="11" t="inlineStr">
         <is>
@@ -10050,17 +10052,17 @@
       </c>
       <c r="L156" s="9">
         <f>IF(B156="","",MONTH(B156))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M156" s="9">
         <f>IF(B156="","",YEAR(B156))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="9">
         <f>IF(B157="","",ROW()-1)</f>
-        <v/>
+        <v>156</v>
       </c>
       <c r="B157" s="10" t="n">
         <v>46241</v>
@@ -10098,7 +10100,7 @@
       </c>
       <c r="J157" s="14">
         <f>IF(OR(H157="",I157=""),"",H157*I157)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K157" s="11" t="inlineStr">
         <is>
@@ -10107,17 +10109,17 @@
       </c>
       <c r="L157" s="9">
         <f>IF(B157="","",MONTH(B157))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M157" s="9">
         <f>IF(B157="","",YEAR(B157))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="9">
         <f>IF(B158="","",ROW()-1)</f>
-        <v/>
+        <v>157</v>
       </c>
       <c r="B158" s="10" t="n">
         <v>46244</v>
@@ -10155,7 +10157,7 @@
       </c>
       <c r="J158" s="14">
         <f>IF(OR(H158="",I158=""),"",H158*I158)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="K158" s="11" t="inlineStr">
         <is>
@@ -10164,17 +10166,17 @@
       </c>
       <c r="L158" s="9">
         <f>IF(B158="","",MONTH(B158))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M158" s="9">
         <f>IF(B158="","",YEAR(B158))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="9">
         <f>IF(B159="","",ROW()-1)</f>
-        <v/>
+        <v>158</v>
       </c>
       <c r="B159" s="10" t="n">
         <v>46244</v>
@@ -10212,7 +10214,7 @@
       </c>
       <c r="J159" s="14">
         <f>IF(OR(H159="",I159=""),"",H159*I159)</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="K159" s="11" t="inlineStr">
         <is>
@@ -10221,17 +10223,17 @@
       </c>
       <c r="L159" s="9">
         <f>IF(B159="","",MONTH(B159))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M159" s="9">
         <f>IF(B159="","",YEAR(B159))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="9">
         <f>IF(B160="","",ROW()-1)</f>
-        <v/>
+        <v>159</v>
       </c>
       <c r="B160" s="10" t="n">
         <v>46244</v>
@@ -10269,7 +10271,7 @@
       </c>
       <c r="J160" s="14">
         <f>IF(OR(H160="",I160=""),"",H160*I160)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K160" s="11" t="inlineStr">
         <is>
@@ -10278,17 +10280,17 @@
       </c>
       <c r="L160" s="9">
         <f>IF(B160="","",MONTH(B160))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M160" s="9">
         <f>IF(B160="","",YEAR(B160))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="9">
         <f>IF(B161="","",ROW()-1)</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="B161" s="10" t="n">
         <v>46245</v>
@@ -10326,7 +10328,7 @@
       </c>
       <c r="J161" s="14">
         <f>IF(OR(H161="",I161=""),"",H161*I161)</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="K161" s="11" t="inlineStr">
         <is>
@@ -10335,17 +10337,17 @@
       </c>
       <c r="L161" s="9">
         <f>IF(B161="","",MONTH(B161))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M161" s="9">
         <f>IF(B161="","",YEAR(B161))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="9">
         <f>IF(B162="","",ROW()-1)</f>
-        <v/>
+        <v>161</v>
       </c>
       <c r="B162" s="10" t="n">
         <v>46249</v>
@@ -10383,7 +10385,7 @@
       </c>
       <c r="J162" s="14">
         <f>IF(OR(H162="",I162=""),"",H162*I162)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K162" s="11" t="inlineStr">
         <is>
@@ -10392,17 +10394,17 @@
       </c>
       <c r="L162" s="9">
         <f>IF(B162="","",MONTH(B162))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M162" s="9">
         <f>IF(B162="","",YEAR(B162))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9">
         <f>IF(B163="","",ROW()-1)</f>
-        <v/>
+        <v>162</v>
       </c>
       <c r="B163" s="10" t="n">
         <v>46250</v>
@@ -10440,7 +10442,7 @@
       </c>
       <c r="J163" s="14">
         <f>IF(OR(H163="",I163=""),"",H163*I163)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K163" s="11" t="inlineStr">
         <is>
@@ -10449,17 +10451,17 @@
       </c>
       <c r="L163" s="9">
         <f>IF(B163="","",MONTH(B163))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M163" s="9">
         <f>IF(B163="","",YEAR(B163))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="9">
         <f>IF(B164="","",ROW()-1)</f>
-        <v/>
+        <v>163</v>
       </c>
       <c r="B164" s="10" t="n">
         <v>46251</v>
@@ -10497,7 +10499,7 @@
       </c>
       <c r="J164" s="14">
         <f>IF(OR(H164="",I164=""),"",H164*I164)</f>
-        <v/>
+        <v>-400</v>
       </c>
       <c r="K164" s="11" t="inlineStr">
         <is>
@@ -10506,17 +10508,17 @@
       </c>
       <c r="L164" s="9">
         <f>IF(B164="","",MONTH(B164))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M164" s="9">
         <f>IF(B164="","",YEAR(B164))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="9">
         <f>IF(B165="","",ROW()-1)</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="B165" s="10" t="n">
         <v>46251</v>
@@ -10554,7 +10556,7 @@
       </c>
       <c r="J165" s="14">
         <f>IF(OR(H165="",I165=""),"",H165*I165)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K165" s="11" t="inlineStr">
         <is>
@@ -10563,17 +10565,17 @@
       </c>
       <c r="L165" s="9">
         <f>IF(B165="","",MONTH(B165))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M165" s="9">
         <f>IF(B165="","",YEAR(B165))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="9">
         <f>IF(B166="","",ROW()-1)</f>
-        <v/>
+        <v>165</v>
       </c>
       <c r="B166" s="10" t="n">
         <v>46251</v>
@@ -10611,7 +10613,7 @@
       </c>
       <c r="J166" s="14">
         <f>IF(OR(H166="",I166=""),"",H166*I166)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K166" s="11" t="inlineStr">
         <is>
@@ -10620,17 +10622,17 @@
       </c>
       <c r="L166" s="9">
         <f>IF(B166="","",MONTH(B166))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M166" s="9">
         <f>IF(B166="","",YEAR(B166))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="9">
         <f>IF(B167="","",ROW()-1)</f>
-        <v/>
+        <v>166</v>
       </c>
       <c r="B167" s="10" t="n">
         <v>46253</v>
@@ -10668,7 +10670,7 @@
       </c>
       <c r="J167" s="14">
         <f>IF(OR(H167="",I167=""),"",H167*I167)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="K167" s="11" t="inlineStr">
         <is>
@@ -10677,17 +10679,17 @@
       </c>
       <c r="L167" s="9">
         <f>IF(B167="","",MONTH(B167))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M167" s="9">
         <f>IF(B167="","",YEAR(B167))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="9">
         <f>IF(B168="","",ROW()-1)</f>
-        <v/>
+        <v>167</v>
       </c>
       <c r="B168" s="10" t="n">
         <v>46254</v>
@@ -10725,7 +10727,7 @@
       </c>
       <c r="J168" s="14">
         <f>IF(OR(H168="",I168=""),"",H168*I168)</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="K168" s="11" t="inlineStr">
         <is>
@@ -10734,17 +10736,17 @@
       </c>
       <c r="L168" s="9">
         <f>IF(B168="","",MONTH(B168))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M168" s="9">
         <f>IF(B168="","",YEAR(B168))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="9">
         <f>IF(B169="","",ROW()-1)</f>
-        <v/>
+        <v>168</v>
       </c>
       <c r="B169" s="10" t="n">
         <v>46255</v>
@@ -10782,7 +10784,7 @@
       </c>
       <c r="J169" s="14">
         <f>IF(OR(H169="",I169=""),"",H169*I169)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="K169" s="11" t="inlineStr">
         <is>
@@ -10791,17 +10793,17 @@
       </c>
       <c r="L169" s="9">
         <f>IF(B169="","",MONTH(B169))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M169" s="9">
         <f>IF(B169="","",YEAR(B169))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="9">
         <f>IF(B170="","",ROW()-1)</f>
-        <v/>
+        <v>169</v>
       </c>
       <c r="B170" s="10" t="n">
         <v>46262</v>
@@ -10839,7 +10841,7 @@
       </c>
       <c r="J170" s="14">
         <f>IF(OR(H170="",I170=""),"",H170*I170)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K170" s="11" t="inlineStr">
         <is>
@@ -10848,17 +10850,17 @@
       </c>
       <c r="L170" s="9">
         <f>IF(B170="","",MONTH(B170))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M170" s="9">
         <f>IF(B170="","",YEAR(B170))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="9">
         <f>IF(B171="","",ROW()-1)</f>
-        <v/>
+        <v>170</v>
       </c>
       <c r="B171" s="10" t="n">
         <v>46263</v>
@@ -10896,7 +10898,7 @@
       </c>
       <c r="J171" s="14">
         <f>IF(OR(H171="",I171=""),"",H171*I171)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K171" s="11" t="inlineStr">
         <is>
@@ -10905,17 +10907,17 @@
       </c>
       <c r="L171" s="9">
         <f>IF(B171="","",MONTH(B171))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M171" s="9">
         <f>IF(B171="","",YEAR(B171))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="9">
         <f>IF(B172="","",ROW()-1)</f>
-        <v/>
+        <v>171</v>
       </c>
       <c r="B172" s="10" t="n">
         <v>46263</v>
@@ -10953,7 +10955,7 @@
       </c>
       <c r="J172" s="14">
         <f>IF(OR(H172="",I172=""),"",H172*I172)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K172" s="11" t="inlineStr">
         <is>
@@ -10962,17 +10964,17 @@
       </c>
       <c r="L172" s="9">
         <f>IF(B172="","",MONTH(B172))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M172" s="9">
         <f>IF(B172="","",YEAR(B172))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="9">
         <f>IF(B173="","",ROW()-1)</f>
-        <v/>
+        <v>172</v>
       </c>
       <c r="B173" s="10" t="n">
         <v>46263</v>
@@ -11010,7 +11012,7 @@
       </c>
       <c r="J173" s="14">
         <f>IF(OR(H173="",I173=""),"",H173*I173)</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K173" s="11" t="inlineStr">
         <is>
@@ -11019,17 +11021,17 @@
       </c>
       <c r="L173" s="9">
         <f>IF(B173="","",MONTH(B173))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M173" s="9">
         <f>IF(B173="","",YEAR(B173))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="9">
         <f>IF(B174="","",ROW()-1)</f>
-        <v/>
+        <v>173</v>
       </c>
       <c r="B174" s="10" t="n">
         <v>46265</v>
@@ -11067,7 +11069,7 @@
       </c>
       <c r="J174" s="14">
         <f>IF(OR(H174="",I174=""),"",H174*I174)</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="K174" s="11" t="inlineStr">
         <is>
@@ -11076,17 +11078,17 @@
       </c>
       <c r="L174" s="9">
         <f>IF(B174="","",MONTH(B174))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M174" s="9">
         <f>IF(B174="","",YEAR(B174))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="9">
         <f>IF(B175="","",ROW()-1)</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="B175" s="10" t="n">
         <v>46267</v>
@@ -11124,7 +11126,7 @@
       </c>
       <c r="J175" s="14">
         <f>IF(OR(H175="",I175=""),"",H175*I175)</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="K175" s="11" t="inlineStr">
         <is>
@@ -11133,17 +11135,17 @@
       </c>
       <c r="L175" s="9">
         <f>IF(B175="","",MONTH(B175))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M175" s="9">
         <f>IF(B175="","",YEAR(B175))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="9">
         <f>IF(B176="","",ROW()-1)</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="B176" s="10" t="n">
         <v>46269</v>
@@ -11181,7 +11183,7 @@
       </c>
       <c r="J176" s="14">
         <f>IF(OR(H176="",I176=""),"",H176*I176)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K176" s="11" t="inlineStr">
         <is>
@@ -11190,17 +11192,17 @@
       </c>
       <c r="L176" s="9">
         <f>IF(B176="","",MONTH(B176))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M176" s="9">
         <f>IF(B176="","",YEAR(B176))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="9">
         <f>IF(B177="","",ROW()-1)</f>
-        <v/>
+        <v>176</v>
       </c>
       <c r="B177" s="10" t="n">
         <v>46270</v>
@@ -11238,7 +11240,7 @@
       </c>
       <c r="J177" s="14">
         <f>IF(OR(H177="",I177=""),"",H177*I177)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="K177" s="11" t="inlineStr">
         <is>
@@ -11247,17 +11249,17 @@
       </c>
       <c r="L177" s="9">
         <f>IF(B177="","",MONTH(B177))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M177" s="9">
         <f>IF(B177="","",YEAR(B177))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="9">
         <f>IF(B178="","",ROW()-1)</f>
-        <v/>
+        <v>177</v>
       </c>
       <c r="B178" s="10" t="n">
         <v>46270</v>
@@ -11295,7 +11297,7 @@
       </c>
       <c r="J178" s="14">
         <f>IF(OR(H178="",I178=""),"",H178*I178)</f>
-        <v/>
+        <v>7200</v>
       </c>
       <c r="K178" s="11" t="inlineStr">
         <is>
@@ -11304,17 +11306,17 @@
       </c>
       <c r="L178" s="9">
         <f>IF(B178="","",MONTH(B178))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M178" s="9">
         <f>IF(B178="","",YEAR(B178))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="9">
         <f>IF(B179="","",ROW()-1)</f>
-        <v/>
+        <v>178</v>
       </c>
       <c r="B179" s="10" t="n">
         <v>46272</v>
@@ -11352,7 +11354,7 @@
       </c>
       <c r="J179" s="14">
         <f>IF(OR(H179="",I179=""),"",H179*I179)</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="K179" s="11" t="inlineStr">
         <is>
@@ -11361,17 +11363,17 @@
       </c>
       <c r="L179" s="9">
         <f>IF(B179="","",MONTH(B179))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M179" s="9">
         <f>IF(B179="","",YEAR(B179))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="9">
         <f>IF(B180="","",ROW()-1)</f>
-        <v/>
+        <v>179</v>
       </c>
       <c r="B180" s="10" t="n">
         <v>46274</v>
@@ -11409,7 +11411,7 @@
       </c>
       <c r="J180" s="14">
         <f>IF(OR(H180="",I180=""),"",H180*I180)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="K180" s="11" t="inlineStr">
         <is>
@@ -11418,17 +11420,17 @@
       </c>
       <c r="L180" s="9">
         <f>IF(B180="","",MONTH(B180))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M180" s="9">
         <f>IF(B180="","",YEAR(B180))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="9">
         <f>IF(B181="","",ROW()-1)</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="B181" s="10" t="n">
         <v>46277</v>
@@ -11466,7 +11468,7 @@
       </c>
       <c r="J181" s="14">
         <f>IF(OR(H181="",I181=""),"",H181*I181)</f>
-        <v/>
+        <v>-450</v>
       </c>
       <c r="K181" s="11" t="inlineStr">
         <is>
@@ -11475,11 +11477,11 @@
       </c>
       <c r="L181" s="9">
         <f>IF(B181="","",MONTH(B181))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M181" s="9">
         <f>IF(B181="","",YEAR(B181))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="182">
@@ -33623,6 +33625,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A1:M1001"/>
   <dataValidations count="7">
     <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -33710,7 +33713,7 @@
       </c>
       <c r="B5" s="9">
         <f>COUNTA(Base!$B$2:$B$1001)</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -33731,11 +33734,11 @@
       </c>
       <c r="B6" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;",Base!$I$2:$I$1001,"")</f>
-        <v/>
-      </c>
-      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="str">
         <f>IF(B6=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
@@ -33751,11 +33754,11 @@
       </c>
       <c r="B7" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"",Base!$I$2:$I$1001,"&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9" t="str">
         <f>IF(B7=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
@@ -33771,11 +33774,11 @@
       </c>
       <c r="B8" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;"&amp;DATE(2020,1,1))+COUNTIFS(Base!$B$2:$B$1001,"&gt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="str">
         <f>IF(B8=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
@@ -33791,11 +33794,11 @@
       </c>
       <c r="B9" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;")-SUMPRODUCT(COUNTIFS(Base!$D$2:$D$1001,Listas!$A$5:$A$34,Base!$B$2:$B$1001,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="str">
         <f>IF(B9=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
@@ -33811,11 +33814,11 @@
       </c>
       <c r="B10" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;")-SUMPRODUCT(COUNTIFS(Base!$C$2:$C$1001,Listas!$E$5:$E$34,Base!$B$2:$B$1001,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="str">
         <f>IF(B10=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
@@ -33831,11 +33834,11 @@
       </c>
       <c r="B11" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;",Base!$K$2:$K$1001,"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="str">
         <f>IF(B11=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
@@ -33851,11 +33854,11 @@
       </c>
       <c r="B12" s="9">
         <f>COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;",Base!$H$2:$H$1001,"")+COUNTIFS(Base!$B$2:$B$1001,"&lt;&gt;",Base!$H$2:$H$1001,0)</f>
-        <v/>
-      </c>
-      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="str">
         <f>IF(B12=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
@@ -33871,11 +33874,11 @@
       </c>
       <c r="B13" s="9">
         <f>SUMPRODUCT(--(COUNTIFS(Base!$B$2:$B$1001,Base!$B$2:$B$1001,Base!$C$2:$C$1001,Base!$C$2:$C$1001,Base!$G$2:$G$1001,Base!$G$2:$G$1001,Base!$I$2:$I$1001,Base!$I$2:$I$1001)&gt;1),--(Base!$B$2:$B$1001&lt;&gt;""))</f>
-        <v/>
-      </c>
-      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="str">
         <f>IF(B13=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
@@ -33892,9 +33895,9 @@
       <c r="B14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="9" t="str">
         <f>IF(B14=0,"OK","Corrigir")</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
@@ -33908,13 +33911,13 @@
           <t>Base pronta?</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="18" t="str">
         <f>IF(COUNTIF(C6:C14,"Corrigir")=0,"Sim: pode analisar","Ainda não: "&amp;COUNTIF(C6:C14,"Corrigir")&amp;" item(ns) para corrigir")</f>
-        <v/>
+        <v>Sim: pode analisar</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="A2:D2"/>
@@ -34065,235 +34068,235 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15">
+      <c r="A8" s="15" t="str">
         <f>IF(Listas!$A$5="","",Listas!$A$5)</f>
-        <v/>
+        <v>Serviço</v>
       </c>
       <c r="B8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="C8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>15300</v>
       </c>
       <c r="D8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>44400</v>
       </c>
       <c r="E8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>29800</v>
       </c>
       <c r="F8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>24600</v>
       </c>
       <c r="G8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>30300</v>
       </c>
       <c r="H8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="I8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>30900</v>
       </c>
       <c r="J8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="K8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M8" s="19">
         <f>IF(Listas!$A$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$5,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N8" s="19">
         <f>IF(A8="","",SUM(B8:M8))</f>
-        <v/>
+        <v>261700</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15">
+      <c r="A9" s="15" t="str">
         <f>IF(Listas!$A$6="","",Listas!$A$6)</f>
-        <v/>
+        <v>Produto</v>
       </c>
       <c r="B9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="C9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>394</v>
       </c>
       <c r="D9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>593</v>
       </c>
       <c r="E9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>977</v>
       </c>
       <c r="F9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="G9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>638</v>
       </c>
       <c r="H9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>347</v>
       </c>
       <c r="I9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>891</v>
       </c>
       <c r="J9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M9" s="19">
         <f>IF(Listas!$A$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$6,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N9" s="19">
         <f>IF(A9="","",SUM(B9:M9))</f>
-        <v/>
+        <v>4325</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15">
+      <c r="A10" s="15" t="str">
         <f>IF(Listas!$A$7="","",Listas!$A$7)</f>
-        <v/>
+        <v>Reembolso</v>
       </c>
       <c r="B10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-600</v>
       </c>
       <c r="E10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="I10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-400</v>
       </c>
       <c r="J10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="K10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M10" s="19">
         <f>IF(Listas!$A$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$7,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N10" s="19">
         <f>IF(A10="","",SUM(B10:M10))</f>
-        <v/>
+        <v>-1400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
+      <c r="A11" s="15" t="str">
         <f>IF(Listas!$A$8="","",Listas!$A$8)</f>
-        <v/>
+        <v>Ajuste</v>
       </c>
       <c r="B11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="C11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="D11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="F11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="H11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-300</v>
       </c>
       <c r="I11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>750</v>
       </c>
       <c r="J11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>-450</v>
       </c>
       <c r="K11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M11" s="19">
         <f>IF(Listas!$A$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$8,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N11" s="19">
         <f>IF(A11="","",SUM(B11:M11))</f>
-        <v/>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
@@ -34536,55 +34539,55 @@
       </c>
       <c r="B16" s="21">
         <f>SUM(B8:B15)</f>
-        <v/>
+        <v>40044</v>
       </c>
       <c r="C16" s="21">
         <f>SUM(C8:C15)</f>
-        <v/>
+        <v>15544</v>
       </c>
       <c r="D16" s="21">
         <f>SUM(D8:D15)</f>
-        <v/>
+        <v>44393</v>
       </c>
       <c r="E16" s="21">
         <f>SUM(E8:E15)</f>
-        <v/>
+        <v>31227</v>
       </c>
       <c r="F16" s="21">
         <f>SUM(F8:F15)</f>
-        <v/>
+        <v>25041</v>
       </c>
       <c r="G16" s="21">
         <f>SUM(G8:G15)</f>
-        <v/>
+        <v>30788</v>
       </c>
       <c r="H16" s="21">
         <f>SUM(H8:H15)</f>
-        <v/>
+        <v>39847</v>
       </c>
       <c r="I16" s="21">
         <f>SUM(I8:I15)</f>
-        <v/>
+        <v>32141</v>
       </c>
       <c r="J16" s="21">
         <f>SUM(J8:J15)</f>
-        <v/>
+        <v>5750</v>
       </c>
       <c r="K16" s="21">
         <f>SUM(K8:K15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L16" s="21">
         <f>SUM(L8:L15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M16" s="21">
         <f>SUM(M8:M15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N16" s="21">
         <f>SUM(N8:N15)</f>
-        <v/>
+        <v>264775</v>
       </c>
     </row>
     <row r="18">
@@ -34622,183 +34625,183 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15">
+      <c r="A20" s="15" t="str">
         <f>IF(Listas!$E$5="","",Listas!$E$5)</f>
-        <v/>
+        <v>Loja Verde</v>
       </c>
       <c r="B20" s="9">
         <f>IF(Listas!$E$5="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C20" s="19">
         <f>IF(Listas!$E$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>42633</v>
       </c>
       <c r="D20" s="19">
         <f>IF(OR(Listas!$E$5="",B20=0),"",C20/B20)</f>
-        <v/>
+        <v>2030.14285714286</v>
       </c>
       <c r="E20" s="23">
-        <f>IF(Listas!$E$5="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$5)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$5)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$5="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$5)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$5)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46270.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15">
+      <c r="A21" s="15" t="str">
         <f>IF(Listas!$E$6="","",Listas!$E$6)</f>
-        <v/>
+        <v>Bistrô 42</v>
       </c>
       <c r="B21" s="9">
         <f>IF(Listas!$E$6="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="C21" s="19">
         <f>IF(Listas!$E$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>31594</v>
       </c>
       <c r="D21" s="19">
         <f>IF(OR(Listas!$E$6="",B21=0),"",C21/B21)</f>
-        <v/>
+        <v>1436.09090909091</v>
       </c>
       <c r="E21" s="23">
-        <f>IF(Listas!$E$6="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$6)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$6)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$6="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$6)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$6)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15">
+      <c r="A22" s="15" t="str">
         <f>IF(Listas!$E$7="","",Listas!$E$7)</f>
-        <v/>
+        <v>Horizonte</v>
       </c>
       <c r="B22" s="9">
         <f>IF(Listas!$E$7="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C22" s="19">
         <f>IF(Listas!$E$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>29890</v>
       </c>
       <c r="D22" s="19">
         <f>IF(OR(Listas!$E$7="",B22=0),"",C22/B22)</f>
-        <v/>
+        <v>1992.66666666667</v>
       </c>
       <c r="E22" s="23">
-        <f>IF(Listas!$E$7="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$7)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$7)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$7="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$7)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$7)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15">
+      <c r="A23" s="15" t="str">
         <f>IF(Listas!$E$8="","",Listas!$E$8)</f>
-        <v/>
+        <v>Padaria do Sol</v>
       </c>
       <c r="B23" s="9">
         <f>IF(Listas!$E$8="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C23" s="19">
         <f>IF(Listas!$E$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>30891</v>
       </c>
       <c r="D23" s="19">
         <f>IF(OR(Listas!$E$8="",B23=0),"",C23/B23)</f>
-        <v/>
+        <v>1817.11764705882</v>
       </c>
       <c r="E23" s="23">
-        <f>IF(Listas!$E$8="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$8)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$8)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$8="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$8)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$8)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46277.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15">
+      <c r="A24" s="15" t="str">
         <f>IF(Listas!$E$9="","",Listas!$E$9)</f>
-        <v/>
+        <v>Clínica Bem-Estar</v>
       </c>
       <c r="B24" s="9">
         <f>IF(Listas!$E$9="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C24" s="19">
         <f>IF(Listas!$E$9="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>50544</v>
       </c>
       <c r="D24" s="19">
         <f>IF(OR(Listas!$E$9="",B24=0),"",C24/B24)</f>
-        <v/>
+        <v>2406.85714285714</v>
       </c>
       <c r="E24" s="23">
-        <f>IF(Listas!$E$9="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$9)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$9)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$9="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$9)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$9)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46270.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15">
+      <c r="A25" s="15" t="str">
         <f>IF(Listas!$E$10="","",Listas!$E$10)</f>
-        <v/>
+        <v>Aurora Móveis</v>
       </c>
       <c r="B25" s="9">
         <f>IF(Listas!$E$10="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C25" s="19">
         <f>IF(Listas!$E$10="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>18450</v>
       </c>
       <c r="D25" s="19">
         <f>IF(OR(Listas!$E$10="",B25=0),"",C25/B25)</f>
-        <v/>
+        <v>1419.23076923077</v>
       </c>
       <c r="E25" s="23">
-        <f>IF(Listas!$E$10="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$10)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$10)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$10="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$10)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$10)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46272.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15">
+      <c r="A26" s="15" t="str">
         <f>IF(Listas!$E$11="","",Listas!$E$11)</f>
-        <v/>
+        <v>Café Central</v>
       </c>
       <c r="B26" s="9">
         <f>IF(Listas!$E$11="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="C26" s="19">
         <f>IF(Listas!$E$11="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>38880</v>
       </c>
       <c r="D26" s="19">
         <f>IF(OR(Listas!$E$11="",B26=0),"",C26/B26)</f>
-        <v/>
+        <v>1944</v>
       </c>
       <c r="E26" s="23">
-        <f>IF(Listas!$E$11="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$11)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$11)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$11="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$11)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$11)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46262.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15">
+      <c r="A27" s="15" t="str">
         <f>IF(Listas!$E$12="","",Listas!$E$12)</f>
-        <v/>
+        <v>Escola Nova Era</v>
       </c>
       <c r="B27" s="9">
         <f>IF(Listas!$E$12="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C27" s="19">
         <f>IF(Listas!$E$12="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
-        <v/>
+        <v>21893</v>
       </c>
       <c r="D27" s="19">
         <f>IF(OR(Listas!$E$12="",B27=0),"",C27/B27)</f>
-        <v/>
+        <v>1990.27272727273</v>
       </c>
       <c r="E27" s="23">
-        <f>IF(Listas!$E$12="","",IFERROR(IF(_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$12)=0,"",_xlfn.MAXIFS(Base!$B$2:$B$1001,Base!$C$2:$C$1001,Listas!$E$12)),""))</f>
-        <v/>
+        <f>IF(Listas!$E$12="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$12)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$12)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v>46251.0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A2:O2"/>
   </mergeCells>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/10-base-limpa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/10-base-limpa.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Nesta planilha só as abas Checklist e Resumo são protegidas; a Base e as Listas ficam livres para você colar dados.</t>
+          <t>Todas as abas são protegidas sem senha. Na Base e nas Listas as células amarelas seguem livres para digitar e colar; o que está bloqueado são as 4.000 fórmulas das colunas calculadas, para uma colagem não apagá-las sem você perceber. Para editar o resto: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
@@ -33628,7 +33628,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A1:M1001"/>
   <dataValidations count="7">
-    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listas!$E$5:$E$34</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -33643,10 +33643,10 @@
     <dataValidation sqref="K2:K1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listas!$D$5:$D$34</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -33940,7 +33940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -34532,272 +34532,2032 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="15">
+        <f>IF(Listas!$A$13="","",Listas!$A$13)</f>
+        <v/>
+      </c>
+      <c r="B16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M16" s="19">
+        <f>IF(Listas!$A$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$13,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N16" s="19">
+        <f>IF(A16="","",SUM(B16:M16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15">
+        <f>IF(Listas!$A$14="","",Listas!$A$14)</f>
+        <v/>
+      </c>
+      <c r="B17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M17" s="19">
+        <f>IF(Listas!$A$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$14,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N17" s="19">
+        <f>IF(A17="","",SUM(B17:M17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15">
+        <f>IF(Listas!$A$15="","",Listas!$A$15)</f>
+        <v/>
+      </c>
+      <c r="B18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M18" s="19">
+        <f>IF(Listas!$A$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$15,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N18" s="19">
+        <f>IF(A18="","",SUM(B18:M18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15">
+        <f>IF(Listas!$A$16="","",Listas!$A$16)</f>
+        <v/>
+      </c>
+      <c r="B19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M19" s="19">
+        <f>IF(Listas!$A$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$16,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N19" s="19">
+        <f>IF(A19="","",SUM(B19:M19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15">
+        <f>IF(Listas!$A$17="","",Listas!$A$17)</f>
+        <v/>
+      </c>
+      <c r="B20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M20" s="19">
+        <f>IF(Listas!$A$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$17,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N20" s="19">
+        <f>IF(A20="","",SUM(B20:M20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15">
+        <f>IF(Listas!$A$18="","",Listas!$A$18)</f>
+        <v/>
+      </c>
+      <c r="B21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M21" s="19">
+        <f>IF(Listas!$A$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$18,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N21" s="19">
+        <f>IF(A21="","",SUM(B21:M21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15">
+        <f>IF(Listas!$A$19="","",Listas!$A$19)</f>
+        <v/>
+      </c>
+      <c r="B22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M22" s="19">
+        <f>IF(Listas!$A$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$19,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N22" s="19">
+        <f>IF(A22="","",SUM(B22:M22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15">
+        <f>IF(Listas!$A$20="","",Listas!$A$20)</f>
+        <v/>
+      </c>
+      <c r="B23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M23" s="19">
+        <f>IF(Listas!$A$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$20,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19">
+        <f>IF(A23="","",SUM(B23:M23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15">
+        <f>IF(Listas!$A$21="","",Listas!$A$21)</f>
+        <v/>
+      </c>
+      <c r="B24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M24" s="19">
+        <f>IF(Listas!$A$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$21,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19">
+        <f>IF(A24="","",SUM(B24:M24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15">
+        <f>IF(Listas!$A$22="","",Listas!$A$22)</f>
+        <v/>
+      </c>
+      <c r="B25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M25" s="19">
+        <f>IF(Listas!$A$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$22,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19">
+        <f>IF(A25="","",SUM(B25:M25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15">
+        <f>IF(Listas!$A$23="","",Listas!$A$23)</f>
+        <v/>
+      </c>
+      <c r="B26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M26" s="19">
+        <f>IF(Listas!$A$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$23,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19">
+        <f>IF(A26="","",SUM(B26:M26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15">
+        <f>IF(Listas!$A$24="","",Listas!$A$24)</f>
+        <v/>
+      </c>
+      <c r="B27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M27" s="19">
+        <f>IF(Listas!$A$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$24,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19">
+        <f>IF(A27="","",SUM(B27:M27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15">
+        <f>IF(Listas!$A$25="","",Listas!$A$25)</f>
+        <v/>
+      </c>
+      <c r="B28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M28" s="19">
+        <f>IF(Listas!$A$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$25,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19">
+        <f>IF(A28="","",SUM(B28:M28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15">
+        <f>IF(Listas!$A$26="","",Listas!$A$26)</f>
+        <v/>
+      </c>
+      <c r="B29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M29" s="19">
+        <f>IF(Listas!$A$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$26,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19">
+        <f>IF(A29="","",SUM(B29:M29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15">
+        <f>IF(Listas!$A$27="","",Listas!$A$27)</f>
+        <v/>
+      </c>
+      <c r="B30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M30" s="19">
+        <f>IF(Listas!$A$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$27,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N30" s="19">
+        <f>IF(A30="","",SUM(B30:M30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15">
+        <f>IF(Listas!$A$28="","",Listas!$A$28)</f>
+        <v/>
+      </c>
+      <c r="B31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M31" s="19">
+        <f>IF(Listas!$A$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$28,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N31" s="19">
+        <f>IF(A31="","",SUM(B31:M31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15">
+        <f>IF(Listas!$A$29="","",Listas!$A$29)</f>
+        <v/>
+      </c>
+      <c r="B32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M32" s="19">
+        <f>IF(Listas!$A$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$29,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N32" s="19">
+        <f>IF(A32="","",SUM(B32:M32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15">
+        <f>IF(Listas!$A$30="","",Listas!$A$30)</f>
+        <v/>
+      </c>
+      <c r="B33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M33" s="19">
+        <f>IF(Listas!$A$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$30,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N33" s="19">
+        <f>IF(A33="","",SUM(B33:M33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15">
+        <f>IF(Listas!$A$31="","",Listas!$A$31)</f>
+        <v/>
+      </c>
+      <c r="B34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M34" s="19">
+        <f>IF(Listas!$A$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$31,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N34" s="19">
+        <f>IF(A34="","",SUM(B34:M34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15">
+        <f>IF(Listas!$A$32="","",Listas!$A$32)</f>
+        <v/>
+      </c>
+      <c r="B35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M35" s="19">
+        <f>IF(Listas!$A$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$32,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N35" s="19">
+        <f>IF(A35="","",SUM(B35:M35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15">
+        <f>IF(Listas!$A$33="","",Listas!$A$33)</f>
+        <v/>
+      </c>
+      <c r="B36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M36" s="19">
+        <f>IF(Listas!$A$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$33,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N36" s="19">
+        <f>IF(A36="","",SUM(B36:M36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15">
+        <f>IF(Listas!$A$34="","",Listas!$A$34)</f>
+        <v/>
+      </c>
+      <c r="B37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,1,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,2,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,3,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,4,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="I37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="J37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="K37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="L37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="M37" s="19">
+        <f>IF(Listas!$A$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$D$2:$D$1001,Listas!$A$34,Base!$L$2:$L$1001,12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="N37" s="19">
+        <f>IF(A37="","",SUM(B37:M37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="21">
-        <f>SUM(B8:B15)</f>
+      <c r="B38" s="21">
+        <f>SUM(B8:B37)</f>
         <v>40044</v>
       </c>
-      <c r="C16" s="21">
-        <f>SUM(C8:C15)</f>
+      <c r="C38" s="21">
+        <f>SUM(C8:C37)</f>
         <v>15544</v>
       </c>
-      <c r="D16" s="21">
-        <f>SUM(D8:D15)</f>
+      <c r="D38" s="21">
+        <f>SUM(D8:D37)</f>
         <v>44393</v>
       </c>
-      <c r="E16" s="21">
-        <f>SUM(E8:E15)</f>
+      <c r="E38" s="21">
+        <f>SUM(E8:E37)</f>
         <v>31227</v>
       </c>
-      <c r="F16" s="21">
-        <f>SUM(F8:F15)</f>
+      <c r="F38" s="21">
+        <f>SUM(F8:F37)</f>
         <v>25041</v>
       </c>
-      <c r="G16" s="21">
-        <f>SUM(G8:G15)</f>
+      <c r="G38" s="21">
+        <f>SUM(G8:G37)</f>
         <v>30788</v>
       </c>
-      <c r="H16" s="21">
-        <f>SUM(H8:H15)</f>
+      <c r="H38" s="21">
+        <f>SUM(H8:H37)</f>
         <v>39847</v>
       </c>
-      <c r="I16" s="21">
-        <f>SUM(I8:I15)</f>
+      <c r="I38" s="21">
+        <f>SUM(I8:I37)</f>
         <v>32141</v>
       </c>
-      <c r="J16" s="21">
-        <f>SUM(J8:J15)</f>
+      <c r="J38" s="21">
+        <f>SUM(J8:J37)</f>
         <v>5750</v>
       </c>
-      <c r="K16" s="21">
-        <f>SUM(K8:K15)</f>
+      <c r="K38" s="21">
+        <f>SUM(K8:K37)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="21">
-        <f>SUM(L8:L15)</f>
+      <c r="L38" s="21">
+        <f>SUM(L8:L37)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="21">
-        <f>SUM(M8:M15)</f>
+      <c r="M38" s="21">
+        <f>SUM(M8:M37)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="21">
-        <f>SUM(N8:N15)</f>
+      <c r="N38" s="21">
+        <f>SUM(N8:N37)</f>
         <v>264775</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Por cliente</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Registros</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Valor no ano</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Ticket médio</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Último registro</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="str">
+    <row r="42">
+      <c r="A42" s="15" t="str">
         <f>IF(Listas!$E$5="","",Listas!$E$5)</f>
         <v>Loja Verde</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B42" s="9">
         <f>IF(Listas!$E$5="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>21</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C42" s="19">
         <f>IF(Listas!$E$5="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$5,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>42633</v>
       </c>
-      <c r="D20" s="19">
-        <f>IF(OR(Listas!$E$5="",B20=0),"",C20/B20)</f>
+      <c r="D42" s="19">
+        <f>IF(OR(Listas!$E$5="",B42=0),"",C42/B42)</f>
         <v>2030.14285714286</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E42" s="23">
         <f>IF(Listas!$E$5="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$5)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$5)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46270.0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="str">
+    <row r="43">
+      <c r="A43" s="15" t="str">
         <f>IF(Listas!$E$6="","",Listas!$E$6)</f>
         <v>Bistrô 42</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B43" s="9">
         <f>IF(Listas!$E$6="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>22</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C43" s="19">
         <f>IF(Listas!$E$6="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$6,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>31594</v>
       </c>
-      <c r="D21" s="19">
-        <f>IF(OR(Listas!$E$6="",B21=0),"",C21/B21)</f>
+      <c r="D43" s="19">
+        <f>IF(OR(Listas!$E$6="",B43=0),"",C43/B43)</f>
         <v>1436.09090909091</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E43" s="23">
         <f>IF(Listas!$E$6="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$6)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$6)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46274.0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="str">
+    <row r="44">
+      <c r="A44" s="15" t="str">
         <f>IF(Listas!$E$7="","",Listas!$E$7)</f>
         <v>Horizonte</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B44" s="9">
         <f>IF(Listas!$E$7="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>15</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C44" s="19">
         <f>IF(Listas!$E$7="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$7,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>29890</v>
       </c>
-      <c r="D22" s="19">
-        <f>IF(OR(Listas!$E$7="",B22=0),"",C22/B22)</f>
+      <c r="D44" s="19">
+        <f>IF(OR(Listas!$E$7="",B44=0),"",C44/B44)</f>
         <v>1992.66666666667</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E44" s="23">
         <f>IF(Listas!$E$7="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$7)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$7)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46255.0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="str">
+    <row r="45">
+      <c r="A45" s="15" t="str">
         <f>IF(Listas!$E$8="","",Listas!$E$8)</f>
         <v>Padaria do Sol</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B45" s="9">
         <f>IF(Listas!$E$8="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>17</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C45" s="19">
         <f>IF(Listas!$E$8="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$8,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>30891</v>
       </c>
-      <c r="D23" s="19">
-        <f>IF(OR(Listas!$E$8="",B23=0),"",C23/B23)</f>
+      <c r="D45" s="19">
+        <f>IF(OR(Listas!$E$8="",B45=0),"",C45/B45)</f>
         <v>1817.11764705882</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E45" s="23">
         <f>IF(Listas!$E$8="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$8)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$8)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46277.0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="str">
+    <row r="46">
+      <c r="A46" s="15" t="str">
         <f>IF(Listas!$E$9="","",Listas!$E$9)</f>
         <v>Clínica Bem-Estar</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B46" s="9">
         <f>IF(Listas!$E$9="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>21</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C46" s="19">
         <f>IF(Listas!$E$9="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$9,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>50544</v>
       </c>
-      <c r="D24" s="19">
-        <f>IF(OR(Listas!$E$9="",B24=0),"",C24/B24)</f>
+      <c r="D46" s="19">
+        <f>IF(OR(Listas!$E$9="",B46=0),"",C46/B46)</f>
         <v>2406.85714285714</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E46" s="23">
         <f>IF(Listas!$E$9="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$9)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$9)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46270.0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="str">
+    <row r="47">
+      <c r="A47" s="15" t="str">
         <f>IF(Listas!$E$10="","",Listas!$E$10)</f>
         <v>Aurora Móveis</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B47" s="9">
         <f>IF(Listas!$E$10="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>13</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C47" s="19">
         <f>IF(Listas!$E$10="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$10,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>18450</v>
       </c>
-      <c r="D25" s="19">
-        <f>IF(OR(Listas!$E$10="",B25=0),"",C25/B25)</f>
+      <c r="D47" s="19">
+        <f>IF(OR(Listas!$E$10="",B47=0),"",C47/B47)</f>
         <v>1419.23076923077</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E47" s="23">
         <f>IF(Listas!$E$10="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$10)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$10)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46272.0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="str">
+    <row r="48">
+      <c r="A48" s="15" t="str">
         <f>IF(Listas!$E$11="","",Listas!$E$11)</f>
         <v>Café Central</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B48" s="9">
         <f>IF(Listas!$E$11="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>20</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C48" s="19">
         <f>IF(Listas!$E$11="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$11,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>38880</v>
       </c>
-      <c r="D26" s="19">
-        <f>IF(OR(Listas!$E$11="",B26=0),"",C26/B26)</f>
+      <c r="D48" s="19">
+        <f>IF(OR(Listas!$E$11="",B48=0),"",C48/B48)</f>
         <v>1944</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E48" s="23">
         <f>IF(Listas!$E$11="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$11)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$11)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46262.0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="str">
+    <row r="49">
+      <c r="A49" s="15" t="str">
         <f>IF(Listas!$E$12="","",Listas!$E$12)</f>
         <v>Escola Nova Era</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B49" s="9">
         <f>IF(Listas!$E$12="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>11</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C49" s="19">
         <f>IF(Listas!$E$12="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$12,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
         <v>21893</v>
       </c>
-      <c r="D27" s="19">
-        <f>IF(OR(Listas!$E$12="",B27=0),"",C27/B27)</f>
+      <c r="D49" s="19">
+        <f>IF(OR(Listas!$E$12="",B49=0),"",C49/B49)</f>
         <v>1990.27272727273</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E49" s="23">
         <f>IF(Listas!$E$12="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$12)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$12)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
         <v>46251.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15">
+        <f>IF(Listas!$E$13="","",Listas!$E$13)</f>
+        <v/>
+      </c>
+      <c r="B50" s="9">
+        <f>IF(Listas!$E$13="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$13,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C50" s="19">
+        <f>IF(Listas!$E$13="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$13,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D50" s="19">
+        <f>IF(OR(Listas!$E$13="",B50=0),"",C50/B50)</f>
+        <v/>
+      </c>
+      <c r="E50" s="23">
+        <f>IF(Listas!$E$13="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$13)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$13)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15">
+        <f>IF(Listas!$E$14="","",Listas!$E$14)</f>
+        <v/>
+      </c>
+      <c r="B51" s="9">
+        <f>IF(Listas!$E$14="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$14,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C51" s="19">
+        <f>IF(Listas!$E$14="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$14,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D51" s="19">
+        <f>IF(OR(Listas!$E$14="",B51=0),"",C51/B51)</f>
+        <v/>
+      </c>
+      <c r="E51" s="23">
+        <f>IF(Listas!$E$14="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$14)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$14)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15">
+        <f>IF(Listas!$E$15="","",Listas!$E$15)</f>
+        <v/>
+      </c>
+      <c r="B52" s="9">
+        <f>IF(Listas!$E$15="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$15,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C52" s="19">
+        <f>IF(Listas!$E$15="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$15,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D52" s="19">
+        <f>IF(OR(Listas!$E$15="",B52=0),"",C52/B52)</f>
+        <v/>
+      </c>
+      <c r="E52" s="23">
+        <f>IF(Listas!$E$15="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$15)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$15)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15">
+        <f>IF(Listas!$E$16="","",Listas!$E$16)</f>
+        <v/>
+      </c>
+      <c r="B53" s="9">
+        <f>IF(Listas!$E$16="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$16,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C53" s="19">
+        <f>IF(Listas!$E$16="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$16,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D53" s="19">
+        <f>IF(OR(Listas!$E$16="",B53=0),"",C53/B53)</f>
+        <v/>
+      </c>
+      <c r="E53" s="23">
+        <f>IF(Listas!$E$16="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$16)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$16)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15">
+        <f>IF(Listas!$E$17="","",Listas!$E$17)</f>
+        <v/>
+      </c>
+      <c r="B54" s="9">
+        <f>IF(Listas!$E$17="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$17,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C54" s="19">
+        <f>IF(Listas!$E$17="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$17,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D54" s="19">
+        <f>IF(OR(Listas!$E$17="",B54=0),"",C54/B54)</f>
+        <v/>
+      </c>
+      <c r="E54" s="23">
+        <f>IF(Listas!$E$17="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$17)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$17)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15">
+        <f>IF(Listas!$E$18="","",Listas!$E$18)</f>
+        <v/>
+      </c>
+      <c r="B55" s="9">
+        <f>IF(Listas!$E$18="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$18,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C55" s="19">
+        <f>IF(Listas!$E$18="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$18,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D55" s="19">
+        <f>IF(OR(Listas!$E$18="",B55=0),"",C55/B55)</f>
+        <v/>
+      </c>
+      <c r="E55" s="23">
+        <f>IF(Listas!$E$18="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$18)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$18)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15">
+        <f>IF(Listas!$E$19="","",Listas!$E$19)</f>
+        <v/>
+      </c>
+      <c r="B56" s="9">
+        <f>IF(Listas!$E$19="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$19,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C56" s="19">
+        <f>IF(Listas!$E$19="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$19,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D56" s="19">
+        <f>IF(OR(Listas!$E$19="",B56=0),"",C56/B56)</f>
+        <v/>
+      </c>
+      <c r="E56" s="23">
+        <f>IF(Listas!$E$19="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$19)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$19)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15">
+        <f>IF(Listas!$E$20="","",Listas!$E$20)</f>
+        <v/>
+      </c>
+      <c r="B57" s="9">
+        <f>IF(Listas!$E$20="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$20,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C57" s="19">
+        <f>IF(Listas!$E$20="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$20,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D57" s="19">
+        <f>IF(OR(Listas!$E$20="",B57=0),"",C57/B57)</f>
+        <v/>
+      </c>
+      <c r="E57" s="23">
+        <f>IF(Listas!$E$20="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$20)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$20)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15">
+        <f>IF(Listas!$E$21="","",Listas!$E$21)</f>
+        <v/>
+      </c>
+      <c r="B58" s="9">
+        <f>IF(Listas!$E$21="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$21,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C58" s="19">
+        <f>IF(Listas!$E$21="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$21,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D58" s="19">
+        <f>IF(OR(Listas!$E$21="",B58=0),"",C58/B58)</f>
+        <v/>
+      </c>
+      <c r="E58" s="23">
+        <f>IF(Listas!$E$21="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$21)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$21)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15">
+        <f>IF(Listas!$E$22="","",Listas!$E$22)</f>
+        <v/>
+      </c>
+      <c r="B59" s="9">
+        <f>IF(Listas!$E$22="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$22,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C59" s="19">
+        <f>IF(Listas!$E$22="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$22,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D59" s="19">
+        <f>IF(OR(Listas!$E$22="",B59=0),"",C59/B59)</f>
+        <v/>
+      </c>
+      <c r="E59" s="23">
+        <f>IF(Listas!$E$22="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$22)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$22)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15">
+        <f>IF(Listas!$E$23="","",Listas!$E$23)</f>
+        <v/>
+      </c>
+      <c r="B60" s="9">
+        <f>IF(Listas!$E$23="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$23,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C60" s="19">
+        <f>IF(Listas!$E$23="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$23,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D60" s="19">
+        <f>IF(OR(Listas!$E$23="",B60=0),"",C60/B60)</f>
+        <v/>
+      </c>
+      <c r="E60" s="23">
+        <f>IF(Listas!$E$23="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$23)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$23)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15">
+        <f>IF(Listas!$E$24="","",Listas!$E$24)</f>
+        <v/>
+      </c>
+      <c r="B61" s="9">
+        <f>IF(Listas!$E$24="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$24,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C61" s="19">
+        <f>IF(Listas!$E$24="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$24,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D61" s="19">
+        <f>IF(OR(Listas!$E$24="",B61=0),"",C61/B61)</f>
+        <v/>
+      </c>
+      <c r="E61" s="23">
+        <f>IF(Listas!$E$24="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$24)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$24)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15">
+        <f>IF(Listas!$E$25="","",Listas!$E$25)</f>
+        <v/>
+      </c>
+      <c r="B62" s="9">
+        <f>IF(Listas!$E$25="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$25,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C62" s="19">
+        <f>IF(Listas!$E$25="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$25,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D62" s="19">
+        <f>IF(OR(Listas!$E$25="",B62=0),"",C62/B62)</f>
+        <v/>
+      </c>
+      <c r="E62" s="23">
+        <f>IF(Listas!$E$25="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$25)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$25)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15">
+        <f>IF(Listas!$E$26="","",Listas!$E$26)</f>
+        <v/>
+      </c>
+      <c r="B63" s="9">
+        <f>IF(Listas!$E$26="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$26,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C63" s="19">
+        <f>IF(Listas!$E$26="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$26,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D63" s="19">
+        <f>IF(OR(Listas!$E$26="",B63=0),"",C63/B63)</f>
+        <v/>
+      </c>
+      <c r="E63" s="23">
+        <f>IF(Listas!$E$26="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$26)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$26)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15">
+        <f>IF(Listas!$E$27="","",Listas!$E$27)</f>
+        <v/>
+      </c>
+      <c r="B64" s="9">
+        <f>IF(Listas!$E$27="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$27,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C64" s="19">
+        <f>IF(Listas!$E$27="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$27,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D64" s="19">
+        <f>IF(OR(Listas!$E$27="",B64=0),"",C64/B64)</f>
+        <v/>
+      </c>
+      <c r="E64" s="23">
+        <f>IF(Listas!$E$27="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$27)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$27)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15">
+        <f>IF(Listas!$E$28="","",Listas!$E$28)</f>
+        <v/>
+      </c>
+      <c r="B65" s="9">
+        <f>IF(Listas!$E$28="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$28,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>IF(Listas!$E$28="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$28,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D65" s="19">
+        <f>IF(OR(Listas!$E$28="",B65=0),"",C65/B65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="23">
+        <f>IF(Listas!$E$28="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$28)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$28)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15">
+        <f>IF(Listas!$E$29="","",Listas!$E$29)</f>
+        <v/>
+      </c>
+      <c r="B66" s="9">
+        <f>IF(Listas!$E$29="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$29,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>IF(Listas!$E$29="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$29,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D66" s="19">
+        <f>IF(OR(Listas!$E$29="",B66=0),"",C66/B66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="23">
+        <f>IF(Listas!$E$29="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$29)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$29)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15">
+        <f>IF(Listas!$E$30="","",Listas!$E$30)</f>
+        <v/>
+      </c>
+      <c r="B67" s="9">
+        <f>IF(Listas!$E$30="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$30,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C67" s="19">
+        <f>IF(Listas!$E$30="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$30,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D67" s="19">
+        <f>IF(OR(Listas!$E$30="",B67=0),"",C67/B67)</f>
+        <v/>
+      </c>
+      <c r="E67" s="23">
+        <f>IF(Listas!$E$30="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$30)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$30)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15">
+        <f>IF(Listas!$E$31="","",Listas!$E$31)</f>
+        <v/>
+      </c>
+      <c r="B68" s="9">
+        <f>IF(Listas!$E$31="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$31,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C68" s="19">
+        <f>IF(Listas!$E$31="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$31,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D68" s="19">
+        <f>IF(OR(Listas!$E$31="",B68=0),"",C68/B68)</f>
+        <v/>
+      </c>
+      <c r="E68" s="23">
+        <f>IF(Listas!$E$31="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$31)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$31)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15">
+        <f>IF(Listas!$E$32="","",Listas!$E$32)</f>
+        <v/>
+      </c>
+      <c r="B69" s="9">
+        <f>IF(Listas!$E$32="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$32,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C69" s="19">
+        <f>IF(Listas!$E$32="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$32,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D69" s="19">
+        <f>IF(OR(Listas!$E$32="",B69=0),"",C69/B69)</f>
+        <v/>
+      </c>
+      <c r="E69" s="23">
+        <f>IF(Listas!$E$32="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$32)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$32)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15">
+        <f>IF(Listas!$E$33="","",Listas!$E$33)</f>
+        <v/>
+      </c>
+      <c r="B70" s="9">
+        <f>IF(Listas!$E$33="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$33,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C70" s="19">
+        <f>IF(Listas!$E$33="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$33,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D70" s="19">
+        <f>IF(OR(Listas!$E$33="",B70=0),"",C70/B70)</f>
+        <v/>
+      </c>
+      <c r="E70" s="23">
+        <f>IF(Listas!$E$33="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$33)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$33)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15">
+        <f>IF(Listas!$E$34="","",Listas!$E$34)</f>
+        <v/>
+      </c>
+      <c r="B71" s="9">
+        <f>IF(Listas!$E$34="","",COUNTIFS(Base!$C$2:$C$1001,Listas!$E$34,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="C71" s="19">
+        <f>IF(Listas!$E$34="","",SUMIFS(Base!$J$2:$J$1001,Base!$C$2:$C$1001,Listas!$E$34,Base!$M$2:$M$1001,$B$4,Base!$K$2:$K$1001,$B$5))</f>
+        <v/>
+      </c>
+      <c r="D71" s="19">
+        <f>IF(OR(Listas!$E$34="",B71=0),"",C71/B71)</f>
+        <v/>
+      </c>
+      <c r="E71" s="23">
+        <f>IF(Listas!$E$34="","",IFERROR(IF(SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$34)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))=0,"",SUMPRODUCT(MAX((Base!$C$2:$C$1001=Listas!$E$34)*(Base!$B$2:$B$1001&lt;&gt;"")*Base!$B$2:$B$1001))),""))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
